--- a/obwieszczenia_masa_upadlosci.xlsx
+++ b/obwieszczenia_masa_upadlosci.xlsx
@@ -422,14 +422,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
@@ -632,32 +632,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260405/00001</t>
+          <t>20260406/00021</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05.04.2026</t>
+          <t>06.04.2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KR1S/GUp/88/2024</t>
+          <t>SZ1S/GUp-s/64/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Katarzyna</t>
+          <t>Agata</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jakubowska</t>
+          <t>Cudzanowska</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skawina, Polska / POLAND</t>
+          <t>Szczecin, Polska / POLAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -667,49 +667,39 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>84020202589</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6751275485</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
-        </is>
-      </c>
+          <t>82070118148</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 5 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Katarzyna Jakubowska, PESEL 84020202589, sygnatura akt KR1S/GUp/88/2024, na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolił syndykowi na sprzedaż z wolnej ręki, po obniżonej cenie, udziału w wysokości 1/2 w prawie własności nieruchomości gruntowej położonej w przy ul. Armii Krajowej 18 w miejscowości Skawina, gm. Skawina, woj. małopolskie, obejmującej działki ewidencyjne nr 5644 i 5645, dla której Sąd Rejonowy w Wieliczce V Zamiejscowy Wydział Ksiąg Wieczystych z s. w Skawinie prowadzi księgę wieczystą nr KR3I/00008006/0 (nr 2.1 w spisie inwentarza), za najwyższą zaoferowaną cenę, nie niższą niż 250.687,50 zł (dwieście pięćdziesiąt tysięcy sześćset osiemdziesiąt siedem złotych 50/100) po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej trzy tygodnie przed terminem rozstrzygnięcia konkursu na co najmniej trzech internetowych portalach branżowych.</t>
+          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Agata Cudzanowska (PESEL 82070118148), sygnatura akt SZ1S/GUp-s/64/2026
+obwieszcza:
+w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Agaty Cudzanowskiej, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjRkOWFkY2YtNjVmZC00NjNkLWJhNGItNGNjOWVmOGUxYjMyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTYwNzc1YjMtNzQyZi00YTBlLTkxNWUtYTAwZjI5MzI5YTU3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260404/00007</t>
+          <t>20260405/00001</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04.04.2026</t>
+          <t>05.04.2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KR1S/GUp-Sędzia-upr/12/2026</t>
+          <t>KR1S/GUp/88/2024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -719,12 +709,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jachyra</t>
+          <t>Jakubowska</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Piotrowice, Polska / POLAND</t>
+          <t>Skawina, Polska / POLAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -734,12 +724,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>76032018700</t>
+          <t>84020202589</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5492062327</t>
+          <t>6751275485</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -754,73 +744,140 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Katarzyna Jachyra (PESEL 76032018700), sygnatura akt KR1S/GUp-Sędzia-upr/12/2026
-obwieszcza: że w skład masy upadłości nie wchodzi wynagrodzenie upadłej Katarzyny Jachyry w całości, począwszy od miesiąca marca 2026 roku.</t>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 5 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Katarzyna Jakubowska, PESEL 84020202589, sygnatura akt KR1S/GUp/88/2024, na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolił syndykowi na sprzedaż z wolnej ręki, po obniżonej cenie, udziału w wysokości 1/2 w prawie własności nieruchomości gruntowej położonej w przy ul. Armii Krajowej 18 w miejscowości Skawina, gm. Skawina, woj. małopolskie, obejmującej działki ewidencyjne nr 5644 i 5645, dla której Sąd Rejonowy w Wieliczce V Zamiejscowy Wydział Ksiąg Wieczystych z s. w Skawinie prowadzi księgę wieczystą nr KR3I/00008006/0 (nr 2.1 w spisie inwentarza), za najwyższą zaoferowaną cenę, nie niższą niż 250.687,50 zł (dwieście pięćdziesiąt tysięcy sześćset osiemdziesiąt siedem złotych 50/100) po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej trzy tygodnie przed terminem rozstrzygnięcia konkursu na co najmniej trzech internetowych portalach branżowych.</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmJkYzg3ZTgtNjM0ZS00MjE3LWI2ZjUtNzRiNzhhNWNhMDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjRkOWFkY2YtNjVmZC00NjNkLWJhNGItNGNjOWVmOGUxYjMyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20260404/00007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>04.04.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>KR1S/GUp-Sędzia-upr/12/2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Jachyra</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Piotrowice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>76032018700</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5492062327</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Katarzyna Jachyra (PESEL 76032018700), sygnatura akt KR1S/GUp-Sędzia-upr/12/2026
+obwieszcza: że w skład masy upadłości nie wchodzi wynagrodzenie upadłej Katarzyny Jachyry w całości, począwszy od miesiąca marca 2026 roku.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmJkYzg3ZTgtNjM0ZS00MjE3LWI2ZjUtNzRiNzhhNWNhMDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>20260404/00012</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>LU1S/GUp-Sędzia-upr/46/2026</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Łukasz</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Maciąg</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Orchówek, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>77110706933</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>5791764391</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Lublin-Wschód w Lublinie z siedzibą w Świdniku</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Łukasz Maciąg , PESEL 77110706933, sygnatura akt LU1S/GUp-Sędzia-upr/46/2026, postanowił:
 I.               wyłączyć z masy upadłości Łukasza Maciąga jako osoby fizycznej nieprowadzącej działalności gospodarczej prawa majątkowe w postaci 100 udziałów w spółce LUBAVA SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ z siedzibą w Warszawie, KRS: 0000620127, o wartości nominalnej 5000 zł (poz. 4.1 spisu inwentarza LU1S/GUp-s/232/2024/154);
@@ -828,65 +885,65 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Lublin-Wschód w Lublinie z siedzibą w Świdniku, IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNjY4ODQ3ZjEtNDM1YS00NDQwLTgwNjQtY2FhMWE3NTdiNTRiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>20260404/00018</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>KR1S/GUp-Sędzia-upr/860/2025</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Małgorzata</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Borkowicz</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Kraków, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>72073114968</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym w sprawie upadłościowej osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Małgorzata Borkowicz (PESEL 72073114968), sygnatura akt KR1S/GUp-Sędzia-upr/860/2025
 obwieszcza:
@@ -894,70 +951,70 @@
 II. ustalić, że w skład masy upadłości nie wchodzą środki zgromadzone na rachunku depozytowym Domu Pomocy Społecznej przy ul. Łanowej 1B w Krakowie w kwocie 2 555,27 zł.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWU0YWI0ZjItNjhjMi00ZWFlLTk4YjMtYzQxYjcyNDY5ZjE5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>20260404/00026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>KR1S/GUp/98/2025</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Edyta</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Pułecka</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Spytkowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>76042612080</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Edyta Pułecka , PESEL 76042612080, sygnatura akt KR1S/GUp/98/2025, postanowił podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki, mienia wchodzącego w skład masy upadłości w postaci udziału w wysokości 1/2 części w prawie własności nieruchomości gruntowej zabudowanej, składającej się z działki ewidencyjnej nr 4883/34, o powierzchni 0,0655 ha, położonej w Spytkowicach, woj. małopolskie, objętej księgą wieczystą numer KR1W/00039427/1, za najwyższą zaoferowaną cenę, nie niższą niż wartość oszacowania tj. za kwotę nie niższą niż 318.000,00 zł (trzysta osiemnaście tysięcy złotych 00/100), po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej dwa tygodnie przed terminem rozstrzygnięcia konkursu w prasie o zasięgu lokalnym oraz na co najmniej dwóch internetowych portalach branżowych.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjU3MWM5NzItYzE3Ni00Yzc2LTliNWItODJkZDFhMzBiMmYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
@@ -972,6 +1029,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/obwieszczenia_masa_upadlosci.xlsx
+++ b/obwieszczenia_masa_upadlosci.xlsx
@@ -422,15 +422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="29" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -510,32 +510,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260406/00017</t>
+          <t>20260407/00001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SZ1S/GUp-s/61/2026</t>
+          <t>BI1B/GUp-Sędzia-upr/44/2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>EWELINA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Banach</t>
+          <t>PODGÓRSKA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Uniemyśl, Polska / POLAND</t>
+          <t>Zbroszki, Polska / POLAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -545,58 +545,62 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>54032407177</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8512599352</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+          <t>94030412982</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Białymstoku</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>VIII Wydział Gospodarczy</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
+          <t>Sąd Rejonowy w Białymstoku, VIII Wydział Gospodarczy, ul. Adama Mickiewicza 103, 15-950 Białystok, obwieszcza, że dokumentem z dnia7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest EWELINA PODGÓRSKA (PESEL 94030412982), sygnatura akt BI1B/GUp-Sędzia-upr/44/2026
 obwieszcza:
-w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
+1. wyłączyć z masy upadłości samochód osobowy Ford Fiesta 1.4 o numerze rejestracyjnym WPU 53694, rok produkcji 2010</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzFjOWJmN2YtOTE1MS00YjRhLTg2NDYtYmY2ZWRlNTA4YWE3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzk4ZjU4M2QtMzRjYi00MDQwLTlhZjAtZTFjNDgxMWFkYWM5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260406/00019</t>
+          <t>20260407/00063</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SZ1S/GUp-s/61/2026</t>
+          <t>KR1S/GUp/70/2023</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Zbigniew</t>
+          <t>Wioletta</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Banach</t>
+          <t>Urbańska-Staszkiewicz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Uniemyśl, Polska / POLAND</t>
+          <t>Kraków, Polska / POLAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -606,58 +610,68 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>54032407177</t>
+          <t>87102204208</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8512599352</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>6751317410</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
-obwieszcza:
-w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha osoby fizycznej nieprowadzącej działalności gospodarczej, został złożony następujący dokument: korekta planu likwidacyjnego.</t>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 25 lutego 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza dłużnika, którym jest Wioletta Urbańska-Staszkiewicz, PESEL 87102204208, prowadzonej pod sygn. akt KR1S/GUp/70/2023, postanowił:
+I. wyłączyć z masy upadłości:
+1) udział spadkowy w wysokości 1/4 w spadku po ojcu upadłej - Kazimierzu Urbańskim, stanowiący ogół praw i obowiązków majątkowych, z wyłączeniem lokalu mieszkalnego objętego księgą wieczystą KR1P/00385735/8 (poz. 4.1 w spisie inwentarza),
+2) udział spadkowy w wysokości 1/2 w spadku po bracie upadłej - Jacku Urbańskim, stanowiący ogół praw i obowiązków majątkowych, z wyłączeniem lokalu mieszkalnego objętego księgą wieczystą KR1P/00385735/8 (poz. 4.2 w spisie inwentarza);
+II. na podstawie art. 357 § 6 k.p.c. w zw. z art. 229 ust. 1 prawa upadłościowego odstąpić od uzasadnienia niniejszego postanowienia wobec uznania w całości zasadności żądania wniosku syndyka i przytoczonych na jego poparcie argumentów przedstawionych szczegółowo w piśmie syndyka z dnia 16 stycznia 2026 roku.</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTNlMWYzOTUtMDQ5Ny00MGNjLTliNDUtMzRjNTRiNDllMTkxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjE4NmQ5YzItZDM1Ny00OGFiLTgwYmQtMmE0MzRjNGQ4ZTZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260406/00021</t>
+          <t>20260407/00067</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06.04.2026</t>
+          <t>07.04.2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SZ1S/GUp-s/64/2026</t>
+          <t>BY1B/GUp-s/107/2026</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Agata</t>
+          <t>NATALIA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cudzanowska</t>
+          <t>MOTYKA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Szczecin, Polska / POLAND</t>
+          <t>Markowice, Polska / POLAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -667,7 +681,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>82070118148</t>
+          <t>91070515565</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -675,209 +689,2179 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
+          <t>Syndyk masy upadłości w sprawie upadłościowej Natalii Motyki nieprowadzącej działalności gospodarczej w upadłości, sygn. akt: BY1B/GUp-s/107/2026, na podstawie art. 491¹¹a prawa upadłościowego, zawiadamia o wyborze sposobu likwidacji składnika masy upadłości w postaci prawa własności lokalu mieszkalnego nr 18, położonego w Markowicach 43 a o pow. 29,56 m2 dla którego Sąd Rejonowy w Mogilnie prowadzi KW nr BY1M/00020182/3 oraz udziału 1/12 w prawie własności nieruchomości zabudowanej położonej w Markowicach, gmina Strzelno, dz. nr 126/7 o pow.415 m2 objętej KW nr BY1M/00019208/2.
+1.     Syndyk sporządził spis inwentarza oraz przyjął wartość prawa własności lokalu mieszkalnego nr 18, położonego w Markowicach 43 a o pow. 29,56 m2 dla którego Sąd Rejonowy w Mogilnie prowadzi KW nr BY1M/00020182/3, zgodnie z operatem szacunkowym sporządzonym przez rzeczoznawcę majątkowego Pawła Michalskiego w kwocie 107.000,00 zł oraz udziału 1/12 w prawie własności nieruchomości zabudowanej położonej w Markowicach, gmina Strzelno, dz. nr 126/7 o pow.415 m2 objętej KW nr BY1M/00019208/2, zgodnie z operatem szacunkowym sporządzonym przez rzeczoznawcę majątkowego Pawła Michalskiego w kwocie 4.667,00 zł.
+2.     W przypadku braku wstrzymania likwidacji przez Sąd, syndyk przystąpi do sprzedaży powyższego majątku z wolnej ręki poprzez umieszczenie ogłoszenia o sprzedaży za cenę nie niższą niż 111.667,00 zł na portalu internetowym OLX.
+3.     W przypadku braku wpływu ofert zakupu w wyznaczonym do tego terminie za powyższą kwotę, syndyk będzie obniżał cenę sprzedaży nieruchomości o kolejne 10 % ceny wyszacowania, po upływie każdego terminu do składania ofert, aż do momentu pozyskania nabywcy.
+Pouczenia:
+Art. 49111a. [Wybór sposobu likwidacji masy upadłości]
+1.   Wyboru sposobu likwidacji masy upadłości dokonuje samodzielnie syndyk w sposób, który umożliwia zaspokojenie wierzycieli w jak największym stopniu, z uwzględnieniem kosztów likwidacji.
+2.   O wyborze sposobu likwidacji nieruchomości oraz wyborze sposobu likwidacji składników masy upadłości, których wartość oszacowania wskazana w spisie inwentarza przekracza pięciokrotność przeciętnego miesięcznego wynagrodzenia w sektorze przedsiębiorstw bez wypłat nagród z zysku w trzecim kwartale roku poprzedzającego złożenie spisu inwentarza, ogłoszonego przez Prezesa Głównego Urzędu Statystycznego, syndyk zawiadamia wierzycieli oraz sąd za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe z wykorzystaniem udostępnianych w tym systemie formularzy. W zawiadomieniu syndyk wskazuje sposób likwidacji oraz minimalną cenę.
+3.   Na skutek skargi na czynności syndyka, o której mowa w art. 49112a, lub z urzędu sąd, w drodze postanowienia, zakazuje syndykowi dokonania likwidacji składnika masy upadłości w wybrany przez syndyka sposób lub za wskazaną minimalną cenę, jeżeli likwidacja byłaby niezgodna z prawem albo prowadziłaby do pokrzywdzenia upadłego lub wierzycieli.
+4.   Przed wydaniem postanowienia, o którym mowa w ust. 3, sąd może wstrzymać dokonanie likwidacji składnika masy upadłości. O wstrzymaniu likwidacji składnika masy upadłości sąd zawiadamia syndyka w dniu wydania postanowienia o wstrzymaniu likwidacji.
+5.   W przypadku braku wstrzymania lub zakazu likwidacji składnika masy upadłości likwidacja może nastąpić po upływie czternastu dni od dnia zawiadomienia, o którym mowa w ust. 2.
+Art. 49112a. [Skarga na czynności syndyka]
+1.   Na czynności syndyka przysługuje skarga do sądu upadłościowego. Dotyczy to także zaniechania przez syndyka dokonania czynności.
+2.   Skargę może złożyć upadły, wierzyciel lub inna osoba, której prawo zostało przez czynności lub zaniechanie syndyka naruszone albo zagrożone.
+3.   Skarga powinna czynić zadość wymaganiom pisma procesowego oraz określać zaskarżoną czynność lub czynność, której zaniechano, jak również wniosek o zmianę, uchylenie lub dokonanie czynności, wraz z uzasadnieniem.
+4.   Skargę wnosi się w terminie siedmiu dni od dnia dokonania czynności, gdy upadły, wierzyciel lub osoba, której prawo zostało przez czynność syndyka naruszone albo zagrożone, była przy czynności obecna lub była o jej terminie zawiadomiona; w innych przypadkach - od dnia zawiadomienia o dokonaniu czynności upadłego, wierzyciela lub osoby, której prawo zostało przez czynność syndyka naruszone albo zagrożone, a w braku zawiadomienia - od dnia powzięcia wiadomości przez skarżącego o dokonanej czynności. Skargę na zaniechanie przez syndyka dokonania czynności wnosi się w terminie siedmiu dni od dnia, w którym skarżący dowiedział się, że czynność miała być dokonana.
+5.   Skargę wnosi się do syndyka, który dokonał zaskarżonej czynności lub zaniechał jej dokonania. Syndyk w terminie trzech dni od dnia otrzymania skargi sporządza uzasadnienie zaskarżonej czynności, o ile nie zostało ono sporządzone wcześniej, albo przyczyn jej zaniechania i przekazuje je wraz ze skargą do właściwego sądu upadłościowego, chyba że skargę w całości uwzględnia. O uwzględnieniu skargi syndyk zawiadamia skarżącego oraz zainteresowanych, których uwzględnienie skargi dotyczy, za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe z wykorzystaniem udostępnianych w tym systemie formularzy.
+6.   Sąd rozpoznaje skargę w terminie siedmiu dni od dnia jej wpływu do sądu, a gdy skarga zawiera braki formalne, które podlegają uzupełnieniu - od dnia jej uzupełnienia.
+7.   Wniesienie skargi nie wstrzymuje postępowania upadłościowego ani dokonania zaskarżonej czynności, chyba że sąd wstrzyma dokonanie czynności.
+8.   Sąd odrzuca skargę wniesioną po upływie przepisanego terminu, nieopłaconą lub z innych przyczyn niedopuszczalną, jak również skargę, której braków nie uzupełniono w terminie. Na postanowienie sądu o odrzuceniu skargi służy zażalenie.
+9.   W razie odrzucenia skargi sąd z urzędu bierze pod uwagę okoliczności wskazane w skardze i w razie potrzeby wydaje syndykowi polecenie dokonania odpowiednich czynności lub zakazuje syndykowi dokonania określonych czynności.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNGM0NjA4YmQtMmZmOS00YTFiLWJiMDgtNDFhMmYwMTI4MGQ4JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260407/00073</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WA2M/GUp-s/374/2024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Szkodzińska</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>00221409523</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>sygn. akt WA2M/GUp-s/374/2024, znak pisma: WA2M/GUp-s/374/2024/167
+Treść obwieszczenia syndyka
+Dnia 3 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Anna Szkodzińska, prowadzonego pod sygn. akt: WA2M/GUp-s/374/2024, złożono do akt opis i szacowanie:
+nieruchomości: udział 3/8 w prawie własności nieruchomości gruntowej, stanowiącej dz. ew. nr 301 położonej w miejscowości Nuna, gm. Nasielsk, pow. nowodworski, woj. mazowieckie. Dla nieruchomości prowadzona jest księga wieczysta nr OS1U/00037691/4 przez Sąd Rejonowy w Pułtusku, IV Wydział Ksiąg Wieczystych.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzc1YzliYjQtY2QxNi00ZDY2LTgyMTktOWZmNGEwMjk3MzRhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260407/00099</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>GD1G/GUp/90/2023</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8421775116</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Gdańsk-Północ w Gdańsku</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 3 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest HIMET SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ SPÓŁKA KOMANDYTOWA, KRS 0000659576, sygnatura akt GD1G/GUp/90/2023, postanowił:
+I. na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego HIMET SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ SPÓŁKA KOMANDYTOWA w postaci:
+wielkogabarytowe 5 osiowe Centrum obróbcze C9-Ciman Mira (nr inw. 1.1), za cenę nie niższą niż kwota 55.370,00 zł netto;
+wielkogabarytowe 4 osiowe centrum obróbcze CHIRON FZ 18 (nr inw. 1.2), za cenę nie niższą niż kwota 6.979,00 zł netto;
+6 kompletów elementów do maszyn HIMLET MAGNETIK stanowiące części stalowe (nr inw. 1.3), za cenę nie niższą niż kwota 100.905,00 zł netto;
+piła taśmowa Pilous (nr inw. 1.5), za cenę nie niższą niż kwota 5.320,00 zł netto;
+maszyna w budowie dla firmy Flader FM Palczewski MIKUS s.c. (nr inw. 1.6) składająca się z: część elektrowrzeciono HITEKO NOWE, wiertarka wielowrzecionowa nowa, obrabiarka pięcioosiowa CNC - nieskończona oraz szafa z elektroniką, za cenę nie niższą niż kwota 166.250,00 zł netto.
+II. wniosek Syndyka z dn. 30 marca 2026 roku (nr dokumentu: GD1G/GUp/90/2023/78) uczynić integralną częścią niniejszego postanowienia.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjY4ZmYzNTAtZjIwNi00YzMwLWI0Y2ItMmZkOTA5ZjcwN2ZhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260407/00105</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WA2M/GUp-s/219/2025</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Dariusz</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Pańczyk</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>71082113535</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>sygn. akt WA2M/GUp-s/219/2025, znak pisma: WA2M/GUp-s/219/2025/51
+Treść obwieszczenia syndyka
+Dnia 3 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Dariusz Pańczyk, prowadzonego pod sygn. akt: WA2M/GUp-s/219/2025, złożono do akt opis i szacowanie:
+nieruchomości: udział 1/2 w prawie własności nieruchomości gruntowej niezabudowanej stanowiącej dz. ew. nr 95/11, obręb 0013, położonej przy ul. Działkowej 20, na terenie miejscowości Warzenko, gmina Przodkowo, powiat kartuski, woj. pomorskiego. Dla nieruchomości prowadzona jest księga wieczysta nr GD1R/00053765/9 przez Sąd Rejonowy w Kartuzach, V Wydział Ksiąg Wieczystych.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjJiZGRjNTEtZDdkMS00MzFmLTgxNTUtMGMxMDBhZWRiZWZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260407/00106</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ZG1E/GUp-Sędzia-upr/24/2026</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Urbanowicz-Mróz</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Zielona Góra, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>88093005320</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Zielonej Górze</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Zielonej Górze, V Wydział Gospodarczy, pl. Słowiański 12, 65-069 Zielona Góra, obwieszcza, że postanowieniem sędziego wyznaczonego z dnia 3 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Paulina Urbanowicz-Mróz (PESEL 88093005320), sygnatura akt ZG1E/GUp-Sędzia-upr/24/2026
+postanowiono:
+na podstawie art. 63 ust. 1c Prawa upadłościowego określić część dochodu upadłej, która nie wchodzi do masy upadłości, w zakresie obejmującym środki pieniężne uzyskane z tytułu zwrotu podatku dochodowego od osób fizycznych upadłej za 2025 r.;
+na podstawie art. 357 § 6 k.p.c. w zw. z art. 229 ust. 1 Prawa upadłościowego uwzględnić w całości wniosek upadłej oraz podzielić zawarte w nim argumenty i odstąpić od uzasadnienia postanowienia, o którym mowa w pkt 1.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Zielonej Górze, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMGQ4YzFiMmEtNzY3Ny00NjFmLWJmMGItY2Q5ZDNlOWNmMDYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260407/00107</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-Sędzia-upr/1502/2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Marcin</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Wdowczyk</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Poznań, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>83061818753</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>6181937126</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>XI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy, ul. Młyńska 1a, 61-729 Poznań, obwieszcza, że dokumentem z dnia 29 stycznia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Marcin Wdowczyk (PESEL 83061818753), sygnatura akt PO1P/GUp-Sędzia-upr/1502/2025
+obwieszcza: oddalić wniosek pełnomocnika upadłego o wyłączenie z masy upadłości udziałów przysługujących upadłemu w następujących spółkach:
+MARWIPOL spółka z ograniczoną odpowiedzialnością, KRS: 0001149696;
+SUNPOWERTECH spółka z ograniczoną odpowiedzialnością, KRS: 0000595478;
+FORTENZA spółka z ograniczoną odpowiedzialnością, KRS: 0001193113.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMDA4MmU0MjEtOTQzZi00MTMxLWJmMjQtMTI0ZjQ4NDE1YzQzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260407/00150</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BB1B/GUp-Sędzia-upr/149/2026</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Szczygieł</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bielsko-Biała, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>55070119686</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bielsku-Białej</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Ewa Szczygieł, PESEL 55070119686, prowadzonej pod sygn. akt BB1B/GUp-Sędzia-upr/149/2026,
+postanowił:
+wyłączyć z masy upadłości całość świadczenia emerytalnego, które obecnie wynosi 3 335,23zł,
+odstąpić od sporządzenia uzasadnienia pkt 1 postanowienia (wniosek upadłego z dnia 1.04.2026r. oraz pismo syndyka z dnia 1.04.2026r.).
+Poucza się, że wierzycielowi przysługuje zażalenie na postanowienie o wyłączeniu z masy upadłości. Zażalenie wnosi się w następujący sposób: wierzyciel może w terminie tygodnia od dnia obwieszczenia postanowienia o wyłączeniu z masy upadłości, wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł. Sąd odrzuci zażalenie jeżeli będzie ono spóźnione, nieopłacone lub dotknięte brakami, które nie zostaną usunięte mimo wezwania. Zażalenie należy skierować do Sądu Upadłościowego - Sądu Rejonowego w Bielsku-Białej, VI Wydział Gospodarczy.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmI3NjU3MmMtNjc2Ni00NGVjLWEwMzYtN2UwMGZjNTMyMzU5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260407/00173</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>KA1K/GUp/16/2023</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Nędza</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Czeladź, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>52060202575</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6251439222</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Katowice Wschód w Katowicach</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Syndyk masy upadłości w postępowaniu upadłościowym osoby fizycznej nieprowadzącej działalności gospodarczej Zbigniewa Nędzy PESEL 52060202575, NIP 6251439222 sygn. akt: KA1K/GUp/16/2023, zawiadamia o sporządzeniu opisu i oszacowania przysługującego upadłemu udziału 1/2 w nieruchomości gruntowej zabudowanej w skład której wchodzą działki ewidencyjne nr 5312/227, 5312/341, 5312/478, tworzące całość funkcjonalną o łącznej powierzchni 1104 m2, położonej przy ul. Czarne 13 w Wiśle, dla której Sąd Rejonowy w Cieszynie, V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o numerze BB1C/00089309/1.
+Z treścią opisu i oszacowania uczestnicy postępowania i osoby zainteresowane mogą zapoznać się po uzyskaniu dostępu do akt postępowania w systemie Krajowego Rejestru Zadłużonych. W terminie tygodnia od daty ukazania się niniejszego obwieszczenia można wnieść do sędziego wyznaczonego zarzuty przeciwko opisowi i oszacowaniu. W postępowaniu upadłościowym pisma procesowe oraz dokumenty, z wyłączeniem pism i dokumentów, o których mowa w art. 216ab, wnosi się wyłącznie za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe z wykorzystaniem udostępnianych w tym systemie formularzy. Pisma oraz dokumenty niewniesione za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe nie wywołują skutków prawnych, jakie ustawa wiąże z wniesieniem pisma albo dokumentu do sądu, tymczasowego nadzorcy sądowego, zarządcy przymusowego, syndyka albo organu, do którego przepisy o syndyku stosuje się odpowiednio.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTk5MTg1OWMtYjNjNC00MWRiLTg2MWMtYzhkMGIwZGVmMTMxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260407/00189</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KI1L/GUp/99/2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Pietrala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kielce, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>68072911392</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>6571000812</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Kielcach</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz w postępowaniu po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza prowadzonym wobec dłużnika, którym jest Mariusz Pietrala (PESEL 68072911392), sygnatura akt KI1L/GUp/99/2025, zarządził:
+o obwieszczeniu, iż syndyk sporządził i przekazał sędziemu-komisarzowi w dniu 3 kwietnia 2026 r. opis i oszacowanie nieruchomości gruntowej położonej w Kielcach przy ul. Skrajnej (dz.ew. nr 504) dla której Sąd Rejonowy w Kielcach VI Wydział Ksiąg Wieczystych prowadzi księgę wieczystą nr KI1L/00051887/0. 
+Zarzuty na opis i oszacowanie wnosi się w terminie tygodnia od dnia obwieszczenia o ich przekazaniu sędziemu-komisarzowi. Zarzuty rozpoznaje sędzia-komisarz.</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzYwY2JhNGMtOGNlYy00M2RkLTllN2MtNTY4MWMwZDQxY2EwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260407/00210</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TR1T/GUp-Sędzia-upr/14/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Zygmunt</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Sokołowski</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tarnów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>58041319052</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8731168876</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Tarnowie</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sędzia wyznaczony obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Zygmunt Sokołowski, PESEL 58041319052, sygnatura akt TR1T/GUp-Sędzia-upr/14/2026, postanowił:
+wyłączyć z masy upadłości dłużnika Zygmunta Sokołowskiego składniki majątkowe w postaci:
+a. 50 (pięćdziesięciu) udziałów w Jazymi spółce z ograniczoną odpowiedzialnością w Krakowie (KRS: 0000503509), oznaczonych w spisie inwentarza numerem 4.1. o wartości nominalnej 2.500 zł (dwa tysiące pięćset złotych);
+b. 50 (pięćdziesięciu) udziałów w Comet Enterprise spółce z ograniczoną odpowiedzialnością w Krakowie (KRS: 0000512359), oznaczonych w spisie inwentarza numerem 4.2. o wartości nominalnej 2.500 zł (dwa tysiące pięćset złotych).
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Tarnowie, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTY5YWYxODMtOWUwOS00YjZkLTk3MmUtZTM2Zjk3ODVhYjJkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260407/00235</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LU1S/GUp-s/28/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Stawiński</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Matczyn, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>83122403151</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7132763879</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>sygn. akt LU1S/GUp-s/28/2026, znak pisma: LU1S/GUp-s/28/2026/41
+Treść obwieszczenia syndyka
+Dnia 6 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Adam Stawiński, prowadzonego pod sygn. akt: LU1S/GUp-s/28/2026, złożono do akt opis i szacowanie:
+nieruchomości gruntowej objętej księgą wieczystą nr KR1I/00047965/1, stanowiąca działki ewid. nr 1584/9 i 1587/5 o łącznej powierzchni 705 m2, zabudowanej budynkiem mieszkalnym jednorodzinnym nr 1084 zrealizowanym w zabudowie wolnostojącej, położonej w Węgrzcach Wielkich, jednostce ewid. Wieliczka - G, obrębie ewid. nr 28, Węgrzce Wielkie, wraz z udziałem w nieruchomości gruntowej ujętej w księdze wieczystej nr KR1I/00045203/8, odpowiadającej działkom ewid. nr 1587/11, 1589/9, 1586/6, 1588/19, 1588/9, stanowiącej drogę wewnętrzną.
+Na opis i oszacowanie można wnosić zarzuty w terminie tygodnia od dnia niniejszego obwieszczenia. Zarzuty wnosi się do sędziego-wyznaczonego na adres: Sąd Rejonowy Lublin –Wschód w Lublinie z siedzibą w Świdniku, IX Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych, ul. Kardynała Stefana Wyszyńskiego 18, 21-040 Świdnik.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTczMmQ1NWEtOThiMi00MzA0LWJjYjgtYTlhZmFhMzUyNWIxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260407/00258</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SW1W/GUp-Sędzia-upr/55/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Mateusz</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Szulc</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Dzierżoniów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>90050916275</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6423134857</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Wałbrzychu</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Mateusz Szulc, PESEL 90050916275, sygnatura akt SW1W/GUp-Sędzia-upr/55/2026, postanowił:
+wyłączyć z masy upadłości: Ford Transit, nr rejestracyjny PZ 0241Y, rok produkcji 2007, nr VIN WF0XXXTTFX7J73858 .
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Wałbrzychu, VI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZDBlNjJlMDAtYzlkYy00OTAzLWI4NTctYWNjYmVlN2M0NDUyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260407/00269</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SW1W/GUp-Sędzia-upr/138/2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Skowera</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Wałbrzych, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>83042309135</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>8862589584</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Wałbrzychu</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Wałbrzychu, VI Wydział Gospodarczy, ul. Juliusza Słowackiego 10,11,11a, 58-300 Wałbrzych, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Piotr Skowera (PESEL 83042309135), sygnatura akt SW1W/GUp-Sędzia-upr/138/2026
+obwieszcza:
+wyłączyć z masy upadłości Piotra Skowery samochód osobowy marki Ford Focus, rok produkcji 2012, nr rejestracyjny DBA32415.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Wałbrzychu, VI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWIzNTk3MzAtYTNhYi00MTY0LWExNjQtZGUxNjI1NjRmNmE2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20260407/00299</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BY1B/GUp/18/2022</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TOMASZ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>GÓRALSKI</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Inowrocław, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>56102807155</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5561014019</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bydgoszczy</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>XV Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest TOMASZ GÓRALSKI, PESEL 56102807155, sygnatura akt BY1B/GUp/18/2022, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia w postaci udziału wynoszącego 1/2 w prawie własności nieruchomości zabudowanej położonej w miejscowości Marcinkowo, gm. Inowrocław:
+a) stanowiącej działkę nr 58/6, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00027957/2, za cenę nie niższą niż 40% wartości oszacowania, tj. 232 400 (dwieście trzydzieści dwa tysiące czterysta) złotych,
+b) stanowiącej działkę nr 58/5, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00057356/8, za cenę nie niższą niż 40% wartości oszacowania, tj. 109 400 (sto dziewięć tysięcy czterysta) złotych,
+c) stanowiącej działkę nr 58/7, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00057357/5, za cenę nie niższą niż 40% wartości oszacowania, tj. 207 600 (dwieście siedem tysięcy sześćset) złotych,
+d) stanowiącej działkę nr 58/8, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00057358/2, za cenę nie niższą niż 40% wartości oszacowania, tj. 149 200 (sto czterdzieści dziewięć tysięcy dwieście) złotych.</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNWY0ZTgzMWEtNjIxNy00ZjhiLWE3MTMtNjBkN2IwNzlhNGFhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20260407/00337</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>OL1O/GUp-Sędzia-upr/143/2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Czechowski</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Szczytno, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>53091201573</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7450002600</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Olsztynie</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Jacek Czechowski, PESEL 53091201573, sygnatura akt OL1O/GUp-Sędzia-upr/143/2026, postanowił:
+wyłączyć z masy upadłości udziały członkowskie upadłego w Banku Spółdzielczym w Szczytnie w wysokości 200 zł.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Olsztynie, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMzdjNWI0NDUtMmYzNC00ZWU1LWFmOWQtYjhmODhiYjllOTFhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20260407/00397</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>KI1L/GUp/29/2024</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sławomir</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Michalec</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kielce, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>63042609855</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>9590217508</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Kielcach</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz w postępowaniu po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza prowadzonym wobec dłużnika, którym jest Sławomir Michalec (PESEL 63042609855), sygnatura akt KI1L/GUp/29/2024, zarządził:
+o obwieszczeniu, iż syndyk sporządził i przekazał sędziemu-komisarzowi w dniu 2 kwietnia 2026 r. opis i oszacowanie udziału wynoszącego 1/2 w prawie współwłasności nieruchomości lokalowej nr 11, przy ul. Karbońskiej 4 w Kielcach.
+Zarzuty na opis i oszacowanie wnosi się w terminie tygodnia od dnia obwieszczenia o ich przekazaniu sędziemu-komisarzowi. Zarzuty rozpoznaje sędzia-komisarz.</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTY4M2NiMGQtZGVjYi00NWFjLWIzYmEtNDg0OWY4NmYyMTMzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20260407/00400</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>OP1O/GUp-Sędzia-upr/21/2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>OLGA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>KUBICA</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Dytmarów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>87062316609</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Opolu</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Sędzia wyznaczony obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest OLGA KUBICA, PESEL 87062316609, prowadzonej pod sygn. akt OP1O/GUp-Sędzia-upr/21/2026, postanowił:
+na podstawie art. 63 ust. 1 pkt 1 w zw. z art. 4912 ust. 1 ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe w zw. z art. 829 pkt 6 k.p.c. stwierdzić, że samochód osobowy marki Volkswagen Turan, numer rejestracyjny OPR6F7, rok produkcji 2010, ujawniony w spisie inwentarza pod numerem 1.1 nie wchodzi w skład masy upadłości.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Opolu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYWIwZGIzZDAtZDQwYS00MWVkLTkzMGMtYzA1MzE3YTExNTJlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20260407/00425</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ZG1E/GUp-s/2/2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Szymański</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Czerwieńsk, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>76010604019</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>9730245078</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Informuje się, że w postępowaniu upadłościowym upadłego, którym jest Tomasz Szymański PESEL 76010604019, prowadzonego pod sygn. akt: ZG1E/GUp-s/2/2026 złożono do akt opis i oszacowanie prawa własności nieruchomości gruntowej niezabudowanej, położonej w Nietkowie, gmina Czerwieńsk, województwo lubuskie, oznaczonej jako działka nr 963/2, dla której prowadzona jest księga wieczysta ZG1E/00099879/8 oraz prawa własności nieruchomości gruntowej niezabudowanej, położonej w Nietkowie, gmina Czerwieńsk, województwo lubuskie, oznaczonej jako działka nr 347/5, dla której prowadzona jest księga wieczysta ZG1E/00008006/4.
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNmY2NGQ3MDctY2E3ZS00YjI4LWJjNDUtYjhmNGQxOTcyYjYxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20260407/00440</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WA2M/GUp/1/2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Jabłoński</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>85021600116</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>7010012994</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>XIX Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Daniel Jabłoński, PESEL 85021600116, sygnatura akt WA2M/GUp/1/2025, postanowił:
+na podstawie art. 4911 ust. 2 w zw. art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego, którym jest Daniel Jabłoński, w postaci należności od Lazzoni Group sp. z o.o. sp.k. (składnik masy upadłości w spisie inwentarza numer 5.1 oraz w uzupełniającym spisie inwentarza nr 5.3) przysługującej solidarnie również Rafałowi Grucy, wobec którego toczy się postępowania upadłościowe pod sygnaturą WA2M/GUp/2/2025, o wartości nominalnej 85.000 zł za 50% ceny wynikającej z oszacowania (wartość rynkowa na podstawie Oszacowania z dnia 20 marca 2026 r. sporządzonego przez biegłego sądowego Wojciecha Makucia, dołączonej do akt postępowania upadłościowego pod nr 147, znak w aktach WA2M/GUp/2/2025/147) , czyli:
+1.   za cenę nie niższą niż 3.128,00 zł (słownie: trzy tysiące sto dwadzieścia osiem złotych) netto, przy czym syndyk przeprowadzi aukcję podaną do publicznej wiadomości, w terminie nie wcześniejszym niż po upływie dwóch tygodni od dnia wydania przez Sędziego-Komisarza niniejszego postanowienia;
+2.   za cenę nie niższą niż 2.346,00 zł (dwa tysiące trzysta czterdzieści sześć złotych) netto, w przypadku gdyby aukcja przeprowadzona w terminie wskazanym w pkt 1, nie doszła do skutku ze względu na brak oferentów, jak również ustalenie, że syndyk przeprowadzi aukcję po obniżonej cenie, podaną do publicznej wiadomości, w terminie nie wcześniejszym niż po upływie dwóch tygodni od upływu terminu przeprowadzenia aukcji wskazanego w pkt 1;</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjllNjJlNDYtMzYzMi00MTNjLWFhMTYtOTBmZGYzNzM2YmI2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20260407/00456</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BY1B/GUp-s/419/2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>MAGDALENA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>KRAJEWSKA</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Niszczewice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>76061002002</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>5562409843</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Maciej Grzelak, obwieszcza, że dokumentem z dnia 31 marca 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest MAGDALENA KRAJEWSKA (PESEL 76061002002), sygnatura akt BY1B/GUp-s/419/2025
+obwieszcza:
+REGULAMIN SPRZEDAŻY Z WOLNEJ RĘKI
+W FORMIE KONKURSU OFERT
+nieruchomości w postępowaniu upadłościowym Magdaleny Krajewskiej oraz Rafała Krajewskiego osób fizycznych
+nieprowadzących działalności gospodarczej
+I. Przedmiot sprzedaży
+1. Przedmiotem sprzedaży są udziały małżonków Magdaleny i Rafała Krajewskich wynoszące po 1/2 w nieruchomości gruntowej zabudowanej budynkiem mieszkalnym, stanowiącej działkę o powierzchni 1,0100 ha o numerze 176/1, położonej w obrębie ewidencyjnym nr 0014 w Niszczewicach, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą o numerze: BY1I/00052618/8 (numer składnika w spisie inwentarza: 2.1 Magdaleny Krajewskiej; numer składnika w spisie inwentarza: 2.1 Rafała Krajewskiego) - udziały są sprzedawane łącznie,
+2. Cena minimalna sprzedaży nieruchomości wynosi 399.000,00 zł (trzysta dziewięćdziesiąt dziewięć tysięcy złotych) – po 199.500,00 zł za każdy udział.
+3. Wpłaty wadium w wysokości 10.000,00 zł należy dokonać na rachunek bankowy masy upadłości o numerze 79 1600 1185 1779 9689 6000 0001. W tytule przelewu należy wskazać „wadium BY1B/GUp-s/419/2025”,
+4. Wadium uważa się za zapłacone jeżeli uznanie rachunku bankowego masy upadłości kwotą wadium nastąpi najpóźniej w dniu 4 maja 2026 roku.
+II. Warunki złożenia oferty i termin wyboru oferenta
+1. Przez złożenie oferty rozumie się złożenie pisemnej oferty na adres doradca restrukturyzacyjny Maciej Grzelak (ul. Gdańska 92/8, 85-021 Bydgoszcz), osobiście lub listownie w zamkniętej kopercie, która to musi wpłynąć najpóźniej do dnia 4 maja 2026 roku do godz. 13:30. W kopercie winna znajdować się kolejna zamknięta koperta zawierająca ofertę, z dopiskiem na tej kopercie „OFERTA, SYGN. AKT BY1B/GUp-s/419/2025, NIE OTWIERAĆ”.
+2. Pisemna oferta winna zawierać co najmniej:
+a) w przypadku osób fizycznych: imię i nazwisko, dokładny adres, numer telefonu oraz numer PESEL, czytelny podpis oferenta,
+w przypadku innych podmiotów niż osoba fizyczna: nazwę oferenta wraz z podaniem jego siedziby, formy organizacyjno-prawnej oraz czytelne podpisy osób upoważnionych do składania oświadczeń w imieniu oferenta wraz z dokumentem wykazującym umocowanie tych osób, dokładny adres, numer NIP lub KRS, numer telefonu,
+b) wskazanie na co składana jest oferta oraz oferowaną cenę nabycia w złotówkach, której wysokość nie może być niższa niż minimalna cena sprzedaży,
+c) w przypadku podmiotu zagranicznego zezwolenie Ministra Spraw Wewnętrznych i Administracji na zakup nieruchomości bądź oświadczenie, że zachodzą wymogi określone w art. 8 ustawy z dnia 24.03.1920 r. o nabywaniu nieruchomości przez cudzoziemców (tekst jednolity: Dz.U.2014.1380),
+d) oświadczenie oferenta, że:
+- zapoznał się z regulaminem sprzedaży, stanem prawnym i technicznym przedmiotu sprzedaży i nie wnosi do nich zastrzeżeń,
+- wyraża zgodę na wyłączenie rękojmi za wady fizyczne i prawne,
+- zobowiązuje się pokryć wszystkie koszty, podatki i opłaty związane z przeniesieniem własności nieruchomości, w tym koszty związane z zawarcie umowy sprzedaży w formie aktu notarialnego,
+- oferent zobowiązuje się dokonać zapłaty całej ceny nie później niż w dniu poprzedzającym zawarcie umowy przenoszącej prawa do nieruchomości,
+e) wszelkie zezwolenia i zgody, jeżeli ze względu na osobę nabywcy są one prawem wymagane (w tym, w przypadku nabywców niebędących osobami fizycznymi, zgodę właściwych organów nabywcy na nabycie przedmiotu sprzedaży, natomiast w przypadku braku konieczności uzyskania takiej zgody od organów nabywcy właściwe dokumenty, które to potwierdzają,
+3. Oferent może, przed upływem terminu do składania ofert, zmienić lub wycofać ofertę. W celu dokonania zmiany lub wycofania oferty, oferent złoży kolejną zapieczętowaną kopertę, oznaczoną jak opisano w punkcie II. 1 z dodaniem słowa: "Zmiana" albo "Wycofanie".
+4. Rozpoznanie złożonych ofert nastąpi w dniu 5 maja 2026 roku o godz. 9:00 w kancelarii syndyka mieszczącej się w Bydgoszczy przy ul. Gdańskiej 92/8. Podstawowe kryterium wyboru oferty stanowi najwyższa zaoferowana cena, równa co najmniej cenie wywoławczej lub wyższa od niej, z tym zastrzeżeniem, że Syndyk może:
+- dokonać swobodnego wyboru oferty albo
+- zarządzić w dniu otwarcia ofert dodatkowo aukcję (licytację) z udziałem oferentów, którzy stawili się na otwarciu ofert, na warunkach wskazanych w części III niniejszego regulaminu.
+III. Zasady przeprowadzenia aukcji (licytacji)
+1. Uczestnikami aukcji (licytacji) są oferenci, którzy stawili się w dacie otwarcia ofert w kancelarii syndyka osobiście lub przez pełnomocników.
+2. Aukcja ma formę ustną i rozpoczyna się od wywołania najwyższej ceny zaproponowanej przez oferentów w ofertach pisemnych.
+3. W trakcie aukcji oferenci zgłaszają ustnie kolejne postąpienia, nie niższe niż o 1.000,00 zł (słownie: jeden tysiąc złotych) dla nieruchomości stanowiącej przedmiot sprzedaży.
+4. Zaoferowana cena przestaje wiązać oferenta, gdy inny oferent zaoferuje wyższą cenę, a ten jej nie przebije.
+5. Syndyk wybiera ofertę uczestnika licytacji (udziela przybicia), który zaoferował najwyższą cenę, której po dwukrotnym powtórzeniu przez Syndyka nikt z uczestników nie podwyższył (trzecie powtórzenie zaoferowanej ceny jest równoznaczne z jej przyjęciem).
+6. W przypadku, gdyby żaden z oferentów nie zaoferował postąpienia tylko pozostał przy cenie wskazanej w ofercie, Syndyk dokona swobodnego wyboru oferty.
+IV. Protokół konkursu ofert i aukcji (licytacji).
+Z przebiegu Konkursu ofert i aukcji (licytacji) syndyk sporządza i podpisuje w dwóch egzemplarzach protokół, dokumentujący podstawowe czynności związane z przebiegiem Konkursu ofert, w tym:
+1. opis przedmiotu Konkursu ofert i aukcji (licytacji);
+2. imię i nazwisko lub nazwę oferentów biorących udział w Konkursie ofert i aukcji (licytacji);
+3. oferowane ceny;
+4. informację o spełnieniu przez oferentów warunków Konkursu ofert;
+5. uzasadnienie odrzucenia oferty;
+6. wskazanie wybranej oferty wraz z uzasadnieniem wyboru – w razie rozstrzygnięcia Konkursu ofert;
+7. wskazanie oferenta, któremu udzielono przybicia – w razie aukcji (licytacji);
+8. zamknięcie Konkursu ofert bez dokonania wyboru oferty
+V. Ogłoszenie wyniku konkursu ofert nastąpi niezwłocznie po jego zakończeniu.
+VI. Postanowienia ogólne
+1. Sprzedaż następuje w postępowaniu upadłościowym i stosownie do art. 313 ust. 1 Prawa upadłościowego ma skutki sprzedaży egzekucyjnej.
+2. Syndyk zastrzega sobie prawo do zmiany warunków lub odwołania procedury sprzedaży na każdym etapie bez podania przyczyny.
+3. Obowiązek zawarcia umowy sprzedaży w terminie do dnia 31 sierpnia 2026 r. pod rygorem utraty wadium.
+4. Oferent przyjmuje do wiadomości, iż na terenie nieruchomości mogą pozostawać przedmioty ruchome niestanowiące składników masy upadłości. Syndyk nie będzie zobowiązany do ich usunięcia lub uprzątnięcia.
+5. W przypadku nieruchomości zamieszkiwanej syndyk nie jest zobowiązany do zapewnienia opuszczenia i opróżnienia lokalu przez osoby dotychczas ten lokal zajmujące.
+6. Złożenie oferty jest równoznaczne z akceptacją niniejszego regulaminu oraz treści ogłoszenia.</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZDZiOThiZjQtMzZlNy00OGE0LWIxNTItZGQ5MTg5M2U4OGMzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20260407/00481</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BB1B/GUp-Sędzia-upr/28/2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Danuta</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Wiercigroch</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bielsko-Biała, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>56122111469</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bielsku-Białej</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bielsku-Białej, VI Wydział Gospodarczy, ul. Wojciecha Bogusławskiego 24, 43-300 Bielsko-Biała, obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Danuta Wiercigroch (PESEL 56122111469), sygnatura akt BB1B/GUp-Sędzia-upr/28/2026
+postanowił:
+1.   na zasadzie art.342a Prawa upadłościowego wydzielić upadłej kwotę 20 400 zł (dwadzieścia tysięcy czterysta złotych) z sumy uzyskanej ze sprzedaży nieruchomości tj. lokalu mieszkalnego położonego w Skoczowie przy ul. Targowej 22 nr księgi wieczystej  BB1C/00089951/6 odpowiadającej czynszowi najmu w wysokości po 1700 zł (jeden tysiąc siedemset złotych) przez okres 12 (dwunastu) miesięcy,
+2.    oddalić wniosek upadłej w pozostałym zakresie.
+Poucza się, że wierzycielowi przysługuje zażalenie na postanowienie o wyłączeniu z masy upadłości. Zażalenie wnosi się w następujący sposób: wierzyciel może w terminie tygodnia od dnia obwieszczenia postanowienia o wyłączeniu z masy upadłości, wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł. Sąd odrzuci zażalenie jeżeli będzie ono spóźnione, nieopłacone lub dotknięte brakami, które nie zostaną usunięte mimo wezwania. Zażalenie należy skierować do Sądu Upadłościowego - Sądu Rejonowego w Bielsku-Białej, VI Wydział Gospodarczy.</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWJhYjEzNDEtYjhiZC00ZjE0LWI2MjUtZjQ4YjMxYTA2NGI2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20260407/00500</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WA2M/GUp-Sędzia-upr/443/2025</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Jabłonka</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>87061208992</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>7822346886</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>XIX Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie, XIX Wydział Gospodarczy, ul. Czerniakowska 100a, 00-454 Warszawa, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Adam Jabłonka (PESEL 87061208992), sygnatura akt WA2M/GUp-Sędzia-upr/443/2025
+postanowił:
+1.     wydzielić upadłemu Adamowi Jabłonka z sumy uzyskanej ze sprzedaży prawa własności nieruchomości gruntowej, stanowiącej działkę ewid. nr 105/7 obręb 0090 o pow. 0,1386 ha, zabudowaną budynkiem mieszkalnym jednorodzinnym, położoną w miejscowości Kępa Kiełpińska 12, w gminie Łomianki, w powiecie warszawskim zachodnim, w województwie mazowieckim, dla której Sąd Rejonowy dla Warszawy-Mokotowa w Warszawie X Wydział Ksiąg Wieczystych prowadzi księgę wieczystą numer WA4M/ 00396385/9, kwotę 72.000,00 zł (siedemdziesiąt dwa tysiące złotych zero groszy) na okres 24 (dwudziestu czterech) miesięcy;
+2.     oddalić wniosek w pozostałym zakresie.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego dla m.st. Warszawy w Warszawie, XIX Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyM2ZmYWUzZmMtMmRkZC00YjY1LThjNzMtMzQzMjRmNTk1ZjdkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20260406/00017</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/61/2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Banach</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Uniemyśl, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>54032407177</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8512599352</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
+obwieszcza:
+w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzFjOWJmN2YtOTE1MS00YjRhLTg2NDYtYmY2ZWRlNTA4YWE3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20260406/00019</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/61/2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Zbigniew</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Banach</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Uniemyśl, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>54032407177</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>8512599352</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
+obwieszcza:
+w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha osoby fizycznej nieprowadzącej działalności gospodarczej, został złożony następujący dokument: korekta planu likwidacyjnego.</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTNlMWYzOTUtMDQ5Ny00MGNjLTliNDUtMzRjNTRiNDllMTkxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20260406/00021</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/64/2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Agata</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cudzanowska</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Szczecin, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>82070118148</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Agata Cudzanowska (PESEL 82070118148), sygnatura akt SZ1S/GUp-s/64/2026
 obwieszcza:
 w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Agaty Cudzanowskiej, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTYwNzc1YjMtNzQyZi00YTBlLTkxNWUtYTAwZjI5MzI5YTU3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20260406/00031</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/68/2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Musialska</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dębina, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>67122407780</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8521357134</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Agnieszka Musialska (PESEL 67122407780), sygnatura akt SZ1S/GUp-s/68/2026
+obwieszcza:
+w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Agnieszki Musialskiej, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTExNGMyNTYtNWM1Zi00ZmExLWEyMWEtM2I3MzU0MmRkMmVmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20260406/00032</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CZ1C/GUp-s/168/2024</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Krzysztof</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Grudziński</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pawonków, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>83110518775</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>sygn. akt CZ1C/GUp-s/168/2024, znak pisma: CZ1C/GUp-s/168/2024/32
+Treść obwieszczenia syndyka
+Dnia 6 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Krzysztof Grudziński, prowadzonego pod sygn. akt: CZ1C/GUp-s/168/2024, złożono do akt opis i szacowanie:
+nieruchomości: udziału 1/2 w prawie własności do lokalu mieszkalnego o powierzchni użytkowej 92,38 m2 dla którego Sąd Rejonowy w Kluczborku, IV Wydział Ksiąg Wieczystych prowadzi księgę wieczysta nr OP1U/00057695/2
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.
+Aby złożyć środek zaskarżenia:
+Zaloguj się do Portalu Użytkowników Zarejestrowanych,
+Na stronie głównej wybierz kafelek "Katalog dokumentów",
+W katalogu dokumentów wybierz kafelek "Środki zaskarżenia",
+Wyszukaj właściwe pismo.
+Właściwym pismem dla tego orzeczenia jest pismo o kodzie zatytułowane: "".
+Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWYxMjljOTMtMDU2NC00NDgwLTk4MzktNTFlMTk1YTczMGZkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20260406/00033</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CZ1C/GUp-s/243/2025</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Stanisław</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Najgebauer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Zawada, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>47050802053</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5730037834</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>sygn. akt CZ1C/GUp-s/243/2025, znak pisma: CZ1C/GUp-s/243/2025/16
+Treść obwieszczenia syndyka
+Dnia 6 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Stanisław Najgebauer, prowadzonego pod sygn. akt: CZ1C/GUp-s/243/2025, złożono do akt opis i szacowanie:
+nieruchomości: udział w 1/2 w prawie własności do nieruchomości składającej się z działek ewidencyjnych nr 310/1, 457, 703, 310/3, 530/2, 659, 776 o łącznej pow. 3,4754 ha dla której Sąd Rejonowy w Myszkowie, V Wydział Ksiąg Wieczystych prowadzi księgę wieczysta nr CZ1M/00005710/7
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.
+Aby złożyć środek zaskarżenia:
+Zaloguj się do Portalu Użytkowników Zarejestrowanych,
+Na stronie głównej wybierz kafelek "Katalog dokumentów",
+W katalogu dokumentów wybierz kafelek "Środki zaskarżenia",
+Wyszukaj właściwe pismo.
+Właściwym pismem dla tego orzeczenia jest pismo o kodzie zatytułowane: "".
+Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyODlkYjkwOTktYmEzOC00NWM2LWI0OTEtNDMxNDVlNzYxZWVkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20260406/00045</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BB1B/GUp-s/513/2025</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Grzegorz</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ziemba</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Hecznarowice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>90032314833</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>9372507846</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>sygn. akt BB1B/GUp-s/513/2025, znak pisma: BB1B/GUp-s/513/2025/27
+Treść obwieszczenia syndyka
+Dnia 6 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Grzegorz Ziemba, prowadzonego pod sygn. akt: BB1B/GUp-s/513/2025, złożono do akt opis i szacowanie udziału wynoszącego 1/8 w prawie własności nieruchomości położonej w Hecznarowicach, gmina Wilamowice, powiat bielski, dla której Sąd Rejonowy w Bielsku-Białej, VII Wydział Ksiąg Wieczystych prowadzi księgę wieczystą nr BB1B/00088834/2, składającej się z działek ewidencyjnych o numerach: 2102 o pow. 0,0972 ha zabudowanej budynkiem mieszkalnym nr 64 przy ul. Stawowej, 26/3 o pow. 0,0421 ha zabudowanej dwoma budynkami niemieszkalnymi (gospodarczymi) oraz 26/12 o pow. 0,1503 ha niezabudowanej</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWYyZGYzNTEtMmI5OC00NjFiLTg5NTQtNWZlNGQ0NzE2ZDZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20260406/00050</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>06.04.2026</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>LD1M/GUp-s/846/2025</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Izabela</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Jurczyk</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Łódź, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>74070301321</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>7262141998</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>sygn. akt LD1M/GUp-s/846/2025, znak pisma: LD1M/GUp-s/846/2025/60
+Treść obwieszczenia syndyka
+Dnia 6 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Izabela Jurczyk, prowadzonego pod sygn. akt: LD1M/GUp-s/846/2025, złożono do akt opis i szacowanie:
+nieruchomości: udział 1/1 w prawie własności nieruchomości gruntowej położonej w miejscowości Wymysłów Piaski, oznaczonej zgodnie z ewidencją gruntów jako działka gruntu nr 50, obręb 0016 Wymysłów Piaski, gmina Dobroń, powiat pabianicki; nieruchomość ma powierzchnię gruntu 0,9667 ha i jest działką niezabudowana, dla której prowadzona jest księga wieczysta nr SR1L/00049949/7 przez Sąd Rejonowy w Łasku, V Wydział Ksiąg Wieczystych; dla nieruchomości wydano nieprawomocną decyzję o warunkach zabudowy 6 (sześciu) domów jednorodzinnych, decyzja została zaskarżona, jest nieprawomocna;
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.
+Aby złożyć środek zaskarżenia:
+Zaloguj się do Portalu Użytkowników Zarejestrowanych,
+Na stronie głównej wybierz kafelek "Katalog dokumentów",
+W katalogu dokumentów wybierz kafelek "Środki zaskarżenia",
+Wyszukaj właściwe pismo.
+Właściwym pismem dla tego orzeczenia jest pismo o kodzie zatytułowane: "".
+Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYTU2OGJiNTktYTE5OS00YjBiLTgzYzQtZWMzZWVmMGE0MDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>20260405/00001</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>05.04.2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>KR1S/GUp/88/2024</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Jakubowska</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Skawina, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>84020202589</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>6751275485</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 5 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Katarzyna Jakubowska, PESEL 84020202589, sygnatura akt KR1S/GUp/88/2024, na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolił syndykowi na sprzedaż z wolnej ręki, po obniżonej cenie, udziału w wysokości 1/2 w prawie własności nieruchomości gruntowej położonej w przy ul. Armii Krajowej 18 w miejscowości Skawina, gm. Skawina, woj. małopolskie, obejmującej działki ewidencyjne nr 5644 i 5645, dla której Sąd Rejonowy w Wieliczce V Zamiejscowy Wydział Ksiąg Wieczystych z s. w Skawinie prowadzi księgę wieczystą nr KR3I/00008006/0 (nr 2.1 w spisie inwentarza), za najwyższą zaoferowaną cenę, nie niższą niż 250.687,50 zł (dwieście pięćdziesiąt tysięcy sześćset osiemdziesiąt siedem złotych 50/100) po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej trzy tygodnie przed terminem rozstrzygnięcia konkursu na co najmniej trzech internetowych portalach branżowych.</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjRkOWFkY2YtNjVmZC00NjNkLWJhNGItNGNjOWVmOGUxYjMyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>20260404/00007</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>KR1S/GUp-Sędzia-upr/12/2026</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Jachyra</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Piotrowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>76032018700</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>5492062327</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Katarzyna Jachyra (PESEL 76032018700), sygnatura akt KR1S/GUp-Sędzia-upr/12/2026
 obwieszcza: że w skład masy upadłości nie wchodzi wynagrodzenie upadłej Katarzyny Jachyry w całości, począwszy od miesiąca marca 2026 roku.</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmJkYzg3ZTgtNjM0ZS00MjE3LWI2ZjUtNzRiNzhhNWNhMDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>20260404/00012</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>LU1S/GUp-Sędzia-upr/46/2026</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Łukasz</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Maciąg</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Orchówek, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>77110706933</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>5791764391</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Lublin-Wschód w Lublinie z siedzibą w Świdniku</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Łukasz Maciąg , PESEL 77110706933, sygnatura akt LU1S/GUp-Sędzia-upr/46/2026, postanowił:
 I.               wyłączyć z masy upadłości Łukasza Maciąga jako osoby fizycznej nieprowadzącej działalności gospodarczej prawa majątkowe w postaci 100 udziałów w spółce LUBAVA SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ z siedzibą w Warszawie, KRS: 0000620127, o wartości nominalnej 5000 zł (poz. 4.1 spisu inwentarza LU1S/GUp-s/232/2024/154);
@@ -885,65 +2869,65 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Lublin-Wschód w Lublinie z siedzibą w Świdniku, IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNjY4ODQ3ZjEtNDM1YS00NDQwLTgwNjQtY2FhMWE3NTdiNTRiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>20260404/00018</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>KR1S/GUp-Sędzia-upr/860/2025</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Małgorzata</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Borkowicz</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Kraków, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>72073114968</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym w sprawie upadłościowej osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Małgorzata Borkowicz (PESEL 72073114968), sygnatura akt KR1S/GUp-Sędzia-upr/860/2025
 obwieszcza:
@@ -951,70 +2935,70 @@
 II. ustalić, że w skład masy upadłości nie wchodzą środki zgromadzone na rachunku depozytowym Domu Pomocy Społecznej przy ul. Łanowej 1B w Krakowie w kwocie 2 555,27 zł.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWU0YWI0ZjItNjhjMi00ZWFlLTk4YjMtYzQxYjcyNDY5ZjE5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>20260404/00026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>KR1S/GUp/98/2025</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Edyta</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Pułecka</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Spytkowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>76042612080</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Edyta Pułecka , PESEL 76042612080, sygnatura akt KR1S/GUp/98/2025, postanowił podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki, mienia wchodzącego w skład masy upadłości w postaci udziału w wysokości 1/2 części w prawie własności nieruchomości gruntowej zabudowanej, składającej się z działki ewidencyjnej nr 4883/34, o powierzchni 0,0655 ha, położonej w Spytkowicach, woj. małopolskie, objętej księgą wieczystą numer KR1W/00039427/1, za najwyższą zaoferowaną cenę, nie niższą niż wartość oszacowania tj. za kwotę nie niższą niż 318.000,00 zł (trzysta osiemnaście tysięcy złotych 00/100), po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej dwa tygodnie przed terminem rozstrzygnięcia konkursu w prasie o zasięgu lokalnym oraz na co najmniej dwóch internetowych portalach branżowych.</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjU3MWM5NzItYzE3Ni00Yzc2LTliNWItODJkZDFhMzBiMmYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
@@ -1030,6 +3014,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/obwieszczenia_masa_upadlosci.xlsx
+++ b/obwieszczenia_masa_upadlosci.xlsx
@@ -422,15 +422,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="31" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="39" customWidth="1" min="6" max="6"/>
     <col width="56" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -510,125 +510,1078 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20260408/00014</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LU1S/GUp/27/2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Andrzej</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Woś</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Opole Lubelskie, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>58091814552</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7170008441</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Lublin-Wschód w Lublinie z siedzibą w Świdniku</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Andrzej Woś, PESEL 58091814552, sygnatura akt LU1S/GUp/27/2025, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe, zezwolić syndykowi masy upadłości upadłego, którym jest Andrzej Woś na sprzedaż z wolnej ręki, na warunkach wskazanych we wniosku syndyka z dnia 30 marca 2026 r., mienia w postaci:
+1)    nieruchomości ujętej w spisie inwentarza pod pozycją 2.1, to jest udziału do ½ w prawie użytkowania wieczystego nieruchomości składającej się z działek gruntu o numerach 429/151 i 429/207 o łącznej powierzchni 10,6916 ha, położonej na gruntach miasta Poniatowa, obręb 1 Poniatowa, dla której to nieruchomości Sąd Rejonowy w Opolu Lubelski, IV Wydział Ksiąg Wieczystych prowadzi księgę wieczystą LU1O/00060980/5 za cenę nie niższą niż 838.435,80 zł (osiemset trzydzieści osiem tysięcy czterysta trzydzieści pięć złotych 80/100) to jest za cenę wynoszącą 60% ceny oszacowania;
+2)    nieruchomości ujętej w spisie inwentarza pod pozycją 2.2, to jest udziału do ½ w prawie użytkowania wieczystego nieruchomości składającej oznaczonej w rejestrze gruntów numerem 429/154 o powierzchni 0,1506 ha, położonej na gruntach miasta Poniatowa, obręb 1 Poniatowa, dla której to nieruchomości Sąd Rejonowy w Opolu Lubelski, IV Wydział Ksiąg Wieczystych prowadzi księgę wieczysta LU1O/00059518/6 za cenę nie niższą niż 11.810,40 zł (jedenaście tysięcy osiemset dziesięć złotych i 40/100) to jest za cenę wynoszącą 60% ceny oszacowania;
+3)    nieruchomości ujętej w spisie inwentarza pod pozycją 2.3, to jest udziału do ¾ w prawie własności nieruchomości oznaczonej w rejestrze gruntów numerem 688 o powierzchni 0,0542 ha (w księdze wieczystej oznaczonej numerem 2172), położonej w Opolu Lubelskim przy ul. Cmentarnej 11a, zabudowanej budynkiem mieszkalnym piętrowym z poddaszem, podpiwniczonym o ujawnionej w ewidencji budynków powierzchni zabudowy 70 m.kw./dla której to nieruchomości Sąd Rejonowy w Opolu Lubelski, IV Wydział Ksiąg Wieczystych prowadzi księgę wieczystą LU1O/00017888/4 za cenę nie niższą niż 222.229,20 zł (dwieście dwadzieścia dwa tysiące dwieście dwadzieścia dziewięć złotych i 20/100) to jest za cenę wynoszącą 60% ceny oszacowania;
+zastrzegając, że kupujący jest zobowiązany wpłacić cenę przed podpisaniem umowy i ponieść koszty związane z zawarciem umowy sprzedaży.</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTcwNjY3MmMtMDRhMy00ZTVlLTllZjEtM2MwYzY1MjViMTdmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260408/00026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LU1S/GUp/16/2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8222404133</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Lublin-Wschód w Lublinie z siedzibą w Świdniku</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest AJ TRANSPORT EXPRESS SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ Spółka z ograniczoną odpowiedzialnością, KRS 0001067875, sygnatura akt LU1S/GUp/16/2025, postanowił:
+na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe zezwolić syndykowi masy upadłości upadłej AJ Transport Express Spółki z ograniczoną odpowiedzialnością z siedzibą w Pogorzelu na sprzedaż z wolnej ręki, na warunkach wskazanych we wniosku syndyka z dnia 23 marca 2026 r., mienia w postaci:
+1)    ciągnika siodłowego Scania S550, nr rej. WS 5767E, nr VIN YS2S4X20002174997, rok prod. 2020 – pozycja nr 1.1 w spisie inwentarza; za cenę niższą od wartości oszacowania wskazanej w spisie inwentarza z oszacowaniem złożonym przez syndyka w dniu 5 grudnia 2025 r. lecz nie niższą od 75 % wartości oszacowania ruchomości, to jest za cenę nie niższą niż 138.190,50 zł (sto trzydzieści osiem tysięcy sto dziewięćdziesiąt złotych pięćdziesiąt groszy),
+2)    naczepy Schmitz, nieposiadającej numeru rejestracyjnego, numer VIN WSM00000005081179, rok prod. 2011 – pozycja 1.2 w spisie inwentarza; za cenę niższą od wartości oszacowania wskazanej w spisie inwentarza z oszacowaniem złożonym przez syndyka w dniu 5 grudnia 2025 r. lecz nie niższą od 75 % wartości oszacowania ruchomości, to jest za cenę nie niższą niż 6.457,50 zł (sześć tysięcy czterysta pięćdziesiąt siedem złotych pięćdziesiąt groszy).</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWZhYzAzODctMTU3YS00YTUxLTk3YWUtMTU0ZGJjYzQzZjYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260408/00030</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>GD1G/GUp/87/2024</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5842736810</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Gdańsk-Północ w Gdańsku</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>VI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Gdańsk-Północ w Gdańsku, VI Wydział Gospodarczy, ul. Piekarnicza 10, 80-126 Gdańsk, obwieszcza, że dokumentem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości dłużnika, którym jest EASTEND SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ Spółka komandytowa (KRS 0000517000), sygnatura akt GD1G/GUp/87/2024 postanawia:
+określić, że 95 udziałów w spółce Domrut Społka z ograniczoną odpowiedzialnością z siedzibą w Gdańsku, nr KRS 0000752780 wchodzi w skład masy upadłości.</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNGNkNzMwNTgtNTRkZC00ZTUyLTg4YjEtMzQxZGQ2OWYyZGM1JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260408/00096</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EL1E/GUp-Sędzia-upr/32/2026</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Grodecka</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Działdowo, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>87072817187</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5711612674</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Elblągu</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Elblągu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych, ul. płk. Stanisława Dąbka 21, 82-300 Elbląg, obwieszcza, że postanowieniem sędziego - wyznaczonego z dnia 8 kwietnia 2026 roku w sprawie osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Magdalena Grodecka (PESEL 87072817187), sygnatura akt EL1E/GUp-Sędzia-upr/32/2026 orzeczono:
+wyłączyć z masy upadłości Magdaleny Grodeckiej – osoby fizycznej nieprowadzącej działalności gospodarczej 95 udziałów w przedsiębiorstwie MADE LINE Spółka z ograniczoną odpowiedzialnością z siedzibą w Działdowie, KRS: 0000682969, NIP: 5711716333 (poz. 4.1. spisu inwentarza).
+UZASADNIENIE
+          Postanowieniem Sądu Rejonowego w Elblągu z dnia 08 kwietnia 2025r. sygn. akt EL1E/GU/44/2025 ogłoszono upadłość wobec Magdaleny Grodeckiej - osoby fizycznej nieprowadzącej działalności gospodarczej, a także ustalono m.in., że postępowanie upadłościowe prowadzone będzie w trybie określonym w art. 491 1 ust 1 Prawa upadłościowego.
+         Syndyk we wniosku z dnia 06 marca 2026 roku wniosła o wyłączenie z masy upadłości 95 udziałów o łącznej 285.000,00 zł należących do upadłej w przedsiębiorstwie MADE LINE Spółce z ograniczoną odpowiedzialnością z siedzibą w Działdowie, KRS: 0000682969, NIP: 5711716333 ( poz. 4.1. spisu inwentarza). Syndyk uzasadniając wniosek wskazała, że Spółka złożyła ostatnie sprawozdanie finansowe w 2023r., w którym zarówno po stronie aktywów, pasywów, jak i rachunku zysków i strat wykazano wartości zerowe. Dodatkowo ustalono, iż Spółka została wykreślona z rejestru podatników VAT w 2021r. Wobec braku dokumentów finansowych i jakiejkolwiek aktywności gospodarczej, biegły uznał, iż nie jest możliwe dokonanie wiarygodnej wyceny przedsiębiorstwa, a wartość udziałów, przy uwzględnieniu istniejącego stanu faktycznego i prawnego, wynosić będzie 0,00 zł. Nadto syndyk wskazała, że sporządzanie wyceny przedmiotowych udziałów byłoby niecelowe, ponieważ koszt operatu w rażący sposób przekroczyłby możliwą do uzyskania cenę sprzedaży, co byłoby nieuzasadnione z punktu widzenia interesu masy upadłości oraz zasad ekonomiki postępowania. Syndyk wskazała, że udziały nie mają żadnej wartości rynkowej, a jednocześnie podjęcie próby ich likwidacji znacznie przedłużą trwanie postępowania upadłościowego, co będzie niekorzystne dla wierzycieli. Dodatkowo syndyka wskazała, że po zmianie przepisów w kodeksie spółek handlowych dotyczące art. 182 1 ksh oraz art. 595 1 ksh, bycie udziałów w spółce jest praktycznie niemożliwe. Zabronione jest bowiem dokonywanie obwieszczeń przez syndyka o konkursach sprzedaży udziałów w spółkach z o.o. z wolnej ręki.  Szukanie oferentów celem złożenia oferty na zakup udziałów w spółce oznaczonemu podmiotowi jest niecelowe z uwagi na przedłużenie postępowania upadłościowego oraz ponoszone koszty przewyższające ewentualną kwotę możliwą do uzyskania.
+        /wniosek syndyka – dokument nr 1/
+        W dniu 12 marca 2026r. zarządzono o poinformowaniu upadłej i wierzycieli o zajęcie stanowiska w kontekście wniosku syndyka i o zobowiązaniu do zajęcia stanowiska w przedmiocie wniosku w terminie 7 dni.
+         /zarządzenie – dokument nr 13/
+           Wierzyciel Naczelnik Urzędu Skarbowego w Przysuszu w piśmie z dnia 18 marca 2026r. wskazał, że wyraża zgodę na wyłączenie z masy udziałów w spółce, zgodnie z wnioskiem syndyka.
+           /pismo wierzyciela – dokument nr 16/
+Wierzyciel Antoni Bronisławski ABSerwis Zakład Mechaniki Pojazdowej w piśmie z dnia 02 kwietnia 2026r. wskazał, że wyraża zgodę na wyłączenie z masy udziałów w spółce, zgodnie z wnioskiem syndyka.
+           /pismo wierzyciela – dokument nr 18/
+Zarówno upadła, jak i pozostali wierzyciele nie zajęli stanowiska w kontekście wniosku syndyka.
+       Zgodnie z treścią art. 315 Pr. Upadł. ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe: „Sędzia – komisarz może wyłączyć określone składniki majątku z masy upadłości, w tym nieruchomości lub jej ułamkową część, jeżeli nie można ich zbyć z zachowaniem przepisów ustawy, a dalsze pozostawanie tych składników majątku w masie upadłości będzie niekorzystne dla wierzycieli z uwagi na obciążenie masy upadłości związanymi z tym kosztami. Na postanowienie sędziego – komisarza przysługuje zażalenie.”
+      W ocenie sędziego - wyznaczonego, wniosek syndyka zasługiwał na uwzględnienie
+     Mając powyższe na uwadze, na mocy art. 315 prawa upadłościowego sędzia – wyznaczona postanowiła wyłączyć z masy upadłości 95 udziałów w przedsiębiorstwie MADE LINE Spółka z ograniczoną odpowiedzialnością z siedzibą w Działdowie, KRS: 0000682969, NIP: 5711716333 ( poz. 4.1. spisu inwentarza), gdyż dotyczy udziałów, które nie znajdą nabywcy. Pozostawienie tych składników majątku w masie upadłości byłoby niekorzystne dla wierzycieli z uwagi na obciążenie masy upadłości związanymi z tym kosztami jak również prowadziłoby to do przedłużenia postępowania.
+         Te argumenty sprawiły, że sędzia wyznaczony orzekł, jak w sentencji postanowienia.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Elblągu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZjE2OWJmNzItNjFjZS00NDJjLWJlZjItMzNiYTI2ZDhjNDk3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260408/00110</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EL1E/GUp/12/2025</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Teresa</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Figat</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Elbląg, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>62070705788</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Elblągu</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Teresa Figat , PESEL 62070705788, sygnatura akt EL1E/GUp/12/2025, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego, którym jest Teresa Figat w postaci udziału o wielkości 1/2 w prawie własności lokalu mieszkalnego nr 44 położonego w Elblągu, przy ul. Królewieckiej 209C, o łącznej powierzchni użytkowej wraz z powierzchnią pomieszczeń przynależnych 34,80 m2, dla którego to prawa Sąd Rejonowy w Elblągu VI Wydział Ksiąg Wieczystych prowadzi księgę wieczystą nr KW EL1E/00062681/2 (numer 2.1 w spisie inwentarza), w następujący sposób: w piątym konkursie ofert za cenę nie niższą niż 53.240,00 zł (słownie: pięćdziesiąt trzy tysiące dwieście czterdzieści złotych 00/100), co stanowi 55% wartości oszacowania, w szóstym konkursie ofert za cenę nie niższą niż 48.400,00 zł (słownie: czterdzieści osiem tysięcy czterysta złotych 00/100), co stanowi 50% wartości oszacowania, w siódmym konkursie ofert za cenę nie niższą niż 43.560,00 zł (słownie: czterdzieści trzy tysiące pięćset sześćdziesiąt złotych 00/100), co stanowi 45% wartości oszacowania, w ósmym konkursie ofert za cenę nie niższą niż niż 38.720,00 zł (słownie: trzydzieści osiem tysięcy siedemset dwadzieścia złotych 00/100), co stanowi 40% wartości oszacowania, w każdym przypadku z tym zastrzeżeniem, że: ogłoszenie o sprzedaży zostanie zamieszczone w co najmniej trzech miejscach ogólnodostępnych, w tym w ogłoszeniowych serwisach internetowych przez co najmniej 30 dni, sprzedaż nastąpi za najwyższą oferowaną cenę, nabywca pokryje wszelkie koszty, podatki i opłaty związane z nabyciem w/w mienia, zaś zapłata całej ceny nastąpi przed podpisaniem umowy sprzedaży na rachunek bankowy masy upadłości.</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMzE5MzNiNTUtM2Y3MC00ZjU0LTkzNDctNDY2Yzg5MDAwYWJkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260408/00152</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>KA1K/GUp-s/276/2026</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Mielnik</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sosnowiec, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>65012703840</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>sygn. akt KA1K/GUp-s/276/2026, znak pisma: KA1K/GUp-s/276/2026/27
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Ewa Mielnik, prowadzonego pod sygn. akt: KA1K/GUp-s/276/2026, złożono do akt opis i oszacowanie określający wartość rynkową oraz wartość dla wymuszonej sprzedaży ułamkowej części nieruchomości w wysokości 1/4 w prawie własności do nieruchomości gruntowej składającej się z działki oznaczonej numerem ewidencyjnym 4743, zabudowanej budynkiem niemieszkalnym, położonej w Sosnowcu przy ulicy gen. Stefana Grota-Roweckiego 155.
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyM2NmMDY2NzItNzYyMy00NGE4LTlkNjgtODY2OWFjZTIyOWZlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260408/00154</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>OL1O/GUp-Sędzia-upr/430/2025</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Kamil</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Duklanowski</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Barczewo, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>92022004139</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1181967113</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Olsztynie</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Sędzia-wyznaczony obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Kamil Duklanowski, PESEL 92022004139, prowadzonej pod sygn. akt OL1O/GUp-Sędzia-upr/430/2025 w przedmiocie wniosku upadłego o wyłączenie pojazdu marki Chevrolet Malibu nr rej. WPN 3ME9, nr VIN: KL1GA69U9CB02216A z masy upadłości postanowił:
+wyłączyć z masy upadłości Kamila Duklanowskiego samochód marki Chevrolet Malibu nr rej. WPN 3ME9, nr VIN: KL1GA69U9CB02216A.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Olsztynie, V Wydział Gospodarczy. Zażalenie wnosi się w następujący sposób w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze należy złożyć wniosek o sporządzenie uzasadnienia i doręczenie odpisu postanowienia wraz z pisemnym uzasadnieniem. We wniosku należy wskazać, czy pisemne uzasadnienie ma dotyczyć całości postanowienia czy jego części, w szczególności poszczególnych objętych nim rozstrzygnięć. Wniosek o doręczenie odpisu postanowienia wraz z pisemnym uzasadnieniem podlega opłacie w wysokości 100,00 zł. Sąd odrzuci wniosek o doręczenie odpisu postanowienia z pisemnym uzasadnieniem, jeżeli będzie on spóźniony, nieopłacony lub dotknięty brakami, które nie zostaną usunięte mimo wezwania. Po doręczeniu odpisu postanowienia wraz z uzasadnieniem na piśmie należy w ciągu tygodnia wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł, przy czym uiszczona już opłata 100,00 zł za sporządzenie uzasadnienia zaliczona zostanie na poczet opłaty od zażalenia. Zażalenie może być wniesione tylko co do tej części postanowienia, co do której zażądano uzasadnienia.</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjI1Nzg4NzMtNzkzNS00NTc2LTg4NmUtNDNlZGQ1ZDA0ODc0JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20260408/00155</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WA2M/GUp-Sędzia-upr/281/2026</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Zofia</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Borowiec</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>01230709981</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5242893033</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>XIX Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Zofia Borowiec, PESEL 01230709981, sygnatura akt WA2M/GUp-Sędzia-upr/281/2026, postanowił:
+na podstawie art. 315 p.u. wyłączyć z masy upadłości Zofii Borowiec udziału wynoszącego 7/24 części prawa własności nieruchomości gruntowej składającej się z działki ewidencyjnej o nr 4/6 o powierzchni 750 m2, zabudowanej budynkiem mieszkalnym jednorodzinnym, położonej w Tarnowie przy ul. H. Marusarz 33C, dla której to nieruchomości prowadzona jest księga wieczysta nr TR1T/00073054/1 (składnik masy upadłości w spisie inwentarza ujawniony pod nr 2.1);
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego dla m.st. Warszawy w Warszawie, XIX Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTE4NWUxZWMtOGM1NS00OWJlLTkxZmItMWI4MDRkY2U4ZTBmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20260408/00166</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp/46/2023</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Regina</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Rosłań</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Maszewo, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>52011311523</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>9551464065</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Szczecin-Centrum w Szczecinie</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>XII Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Regina Rosłań, PESEL 52011311523, sygnatura akt SZ1S/GUp/46/2023, postanowił:
+na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego, którym jest Regina Rosłań, w postaci:
+1. nieruchomości niezabudowanej, położonej w Załomiu, ul. Magnolii, działka ewidencyjna wydzielona nr 133/11 (droga), dla której Sąd Rejonowy w Goleniowie V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą Kw nr SZ1O/00051900/0, poz 2.7 spisu inwentarza za cenę nie niższą niż 5% wartości szacunkowej tj. 150 zł (sto pięćdziesiąt złotych);
+2. nieruchomości niezabudowanej, położonej w Załomiu, ul. Magnolii, działka ewidencyjna nr 133/3 (droga), dla której Sąd Rejonowy w Goleniowie V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą Kw nr SZ1O/00051901/7, poz. 2.8 spisu inwentarza za cenę nie niższą niż 5% wartości szacunkowej tj. 450 zł (czterysta pięćdziesiąt złotych);
+3. nieruchomości niezabudowanej, położonej w Załomiu, ul. Dębowa, działka ewidencyjna nr 131/66 (droga), dla której Sąd Rejonowy w Goleniowie V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą Kw nr SZ10/00051899/9, poz. 2.9 spisu inwentarza za cenę nie niższą niż 5 % wartości szacunkowej tj. 1.300 zł (jeden tysiąc trzysta złotych)
+przy czym:
+a) sprzedaż odbędzie się w trybie konkursu ofert na zasadach określonych przez syndyka;
+b) o konkursie ofert należy obwieścić co najmniej w Internecie na portalach (co najmniej dwóch) z ogłoszeniami o sprzedaży nieruchomości;
+c) pozostałe warunki konkursu zostaną ustalone przez syndyka.
+Pouczenie:
+Na niniejsze postanowienie nie przysługuje zażalenie.</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTBhOTg4NzYtY2I4ZC00YzVhLWFjZDQtNmJiZTA3ZmJhYzYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20260408/00180</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>RZ1Z/GUp-s/16/2026</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Genowefa</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Tęczar</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Boguchwała, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>57060619202</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>sygn. akt RZ1Z/GUp-s/16/2026, znak pisma: RZ1Z/GUp-s/16/2026/34
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Genowefa Tęczar, prowadzonego pod sygn. akt: RZ1Z/GUp-s/16/2026, złożono do akt opis i szacowanie:
+nieruchomości: w postaci działki ewidencyjnej nr 541/6 o powierzchni 1800 m2, obręb 0001 Boguchwała, dla której prowadzona jest księga wieczysta RZ1Z/00004897/8 prowadzona przez Sąd Rejonowy w Rzeszowie, VII Wydział Ksiąg Wieczystych.. Działka zabudowana wolnostojącym budynkiem mieszkalnym jednorodzinnym o powierzchni zabudowy 112 mkw w przeciętnym stanie technicznym i przeciętnym standardzie wykończenia, budynkiem mieszkalnym o powierzchni zabudowy 32 mkw w niskim stanie technicznym i niskim standardzie wykończenia oraz budynkiem gospodarczym o powierzchni zabudowy 11 mkw.</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNWZjYzE5MjItNzJmYi00NjlmLTg2NjMtMjNiYjFkZjI2YWQ1JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20260408/00184</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LU1S/GUp-s/64/2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Biegański</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Hańsk Pierwszy, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>73032906875</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9930537578</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>sygn. akt LU1S/GUp-s/64/2025, znak pisma: LU1S/GUp-s/64/2025/59
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Mariusz Biegański, prowadzonego pod sygn. akt: LU1S/GUp-s/64/2025, złożono do akt opis i szacowanie:
+nieruchomości: udziału wynoszącego 1/2 w nieruchomości gruntowej stanowiącej przedmiot prawa własności zabudowanej budynkiem mieszkalnym z towarzyszącą zabudową gospodarczą położonej przy ulicy Parczewskiej 28 w miejscowości Hańsk Pierwszy, powiat włodawski. Opis i oszacowanie jest dostępny w aktach sprawy o sygn. akt LU1S/GUp-s/64/2025 (dokument nr 56)</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyM2FmZTA2OTUtNzUzMy00OGViLTgwMGQtMzlhOGQ3MGYwODhlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20260408/00193</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-Sędzia-upr/383/2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Kęsy</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ryczywół, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>99010501384</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>XI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy, ul. Młyńska 1a, 61-729 Poznań, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Paulina Kęsy (PESEL 99010501384), sygnatura akt PO1P/GUp-Sędzia-upr/383/2026
+postanowił oddalić wniosek o wyłączenie z masy upadłości telewizora marki Samsung.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYzQ2ZjEzZGItYTQ1ZC00ZTkwLThmMjItYTNjODM2YmRlMmFlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20260408/00200</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/58/2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Joanna</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Falender</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dziwnów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>73041405581</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>9860056795</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Krzysztof Andrzej Kaczmarek, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Joanna Falender (PESEL 73041405581), sygnatura akt SZ1S/GUp-s/58/2026
+obwieszcza: do akt postępowania SZ1S/GUp-s/58/2026 syndyk złożył spis inwentarza oraz plan likwidacyjny wraz z preliminarzem wydatków.</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMTI1YWI2MzItY2RkOC00ODcyLThmY2ItMTIzY2IzMGIxMjhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20260408/00242</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WA1M/GUp/7/2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5252533460</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>XVIII Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 8 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest MENNICA FINANCE Spółka akcyjna, KRS 0000427318, sygnatura akt WA1M/GUp/7/2026, postanowił:
+podstawie art. 311 ust. 1 i art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003 r. – Prawo upadłościowe, zezwolić syndykowi masy upadłości na sprzedaż z wolnej ręki nieruchomości wchodzących w skład masy upadłości Mennica Finance spółki akcyjnej z siedzibą w Warszawie, tj.:
+prawa własności nieruchomości gruntowej niezabudowanej, działki o numerze ewidencyjnym numer 262/2 położonej w obrębie ewidencyjnym numer 0007 Jora Wielka w miejscowości Jora Wielka, gmina Mikołajki, powiat mrągowski, województwo warmińsko-mazurskie, dla której to Sąd Rejonowy w Mrągowie, IV Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o numerze OL1M/00028184/6 wchodzącej w skład masy upadłości Mennica Finance spółki akcyjnej, za cenę nie niższą niż 596.000,00 zł netto (słownie: pięćset dziewięćdziesiąt sześć tysięcy złotych);
+w przypadku braku ofert na nabycie nieruchomości wskazanej w punkcie 1. postanowienia za wskazaną w tym punkcie cenę w ciągu miesiąca od publikacji ogłoszeń o sprzedaży, zezwolić syndykowi masy upadłości na sprzedaż z wolnej ręki prawa własności nieruchomości szczegółowo opisanej w punkcie 1. postanowienia za cenę nie niższą niż 477.000,00 zł netto (słownie: czterysta siedemdziesiąt siedem tysięcy złotych);
+prawa własności nieruchomości gruntowej niezabudowanej, działki numer 82/2 położonej w obrębie ewidencyjnym numer 0008 Kal, w miejscowości Kal, gmina Węgorzewo, powiat węgorzewski, województwo warmińsko-mazurskie, dla której Sąd Rejonowy w Giżycku, VII Zamiejscowy Wydział Ksiąg Wieczystych w Węgorzewie prowadzi księgę wieczystą o numerze OL2G/00020107/8 wchodzącej w skład masy upadłości Mennica Finance spółki akcyjnej, za cenę nie niższą niż 1.660.000,00 zł netto (słownie: jeden milion sześćset sześćdziesiąt tysięcy złotych),;
+w przypadku braku ofert na nabycie nieruchomości wskazanej w punkcie 3. postanowienia za wskazaną w tym punkcie cenę w ciągu miesiąca od publikacji ogłoszeń o sprzedaży, zezwolić syndykowi masy upadłości na sprzedaż z wolnej ręki prawa własności nieruchomości szczegółowo opisanej w punkcie 3. postanowienia za cenę nie niższą niż 1.328.000,00 zł netto (słownie: jeden milion trzysta dwadzieścia osiem tysięcy złotych);
+określić ponadto następujące warunki zbycia nieruchomości:
+-       o sprzedaży obwieścić w Internecie na co najmniej trzech platformach ogłoszeniowych przeznaczonych do sprzedaży nieruchomości;
+-       w razie zgłoszenia się więcej niż jednego oferenta, syndyk powinien powiadomić o tym (w dowolnej formie) wszystkie osoby zainteresowane, wyznaczyć oferentom termin aukcji, w której ceną wywoławczą będzie najwyższa zaproponowana kwota;
+-       wybór oferty zostanie dokonany przy zastosowaniu kryterium ceny;
+-       zawarcie umowy sprzedaży może nastąpić nie wcześniej niż po upływie 14 dni od ukazania się ogłoszenia w Internecie.</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMDZiMDNkZmMtYmNjYy00ZTg4LTliNjEtZjJkNDg4NDliMzBhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20260408/00293</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>08.04.2026</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ZG1E/GUp-s/286/2023</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Leszek</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Napieralski</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Nowa Sól, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>79050206711</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sygn. akt ZG1E/GUp-s/286/2023, znak pisma: ZG1E/GUp-s/286/2023/28
+Treść obwieszczenia syndyka
+Dnia 8 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Leszek Napieralski, prowadzonego pod sygn. akt: ZG1E/GUp-s/286/2023, złożono do akt opis i szacowanie:
+nieruchomości: zabudowanej położonej w miejscowości Przyborów ul. Podwale 1 gmina Nowa Sól oznaczonej działką nr 126/1 w której upadły posiada udział 1/8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMzYwMjY5OTgtZjE4ZC00ZDU0LWE3MTAtYzZhM2U0ZGQxZTM0JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>20260407/00001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>BI1B/GUp-Sędzia-upr/44/2026</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>EWELINA</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>PODGÓRSKA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Zbroszki, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
         <is>
           <t>94030412982</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Białymstoku</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Białymstoku, VIII Wydział Gospodarczy, ul. Adama Mickiewicza 103, 15-950 Białystok, obwieszcza, że dokumentem z dnia7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest EWELINA PODGÓRSKA (PESEL 94030412982), sygnatura akt BI1B/GUp-Sędzia-upr/44/2026
 obwieszcza:
 1. wyłączyć z masy upadłości samochód osobowy Ford Fiesta 1.4 o numerze rejestracyjnym WPU 53694, rok produkcji 2010</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzk4ZjU4M2QtMzRjYi00MDQwLTlhZjAtZTFjNDgxMWFkYWM5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>20260407/00063</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>KR1S/GUp/70/2023</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Wioletta</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Urbańska-Staszkiewicz</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Kraków, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
         <is>
           <t>87102204208</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>6751317410</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 25 lutego 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza dłużnika, którym jest Wioletta Urbańska-Staszkiewicz, PESEL 87102204208, prowadzonej pod sygn. akt KR1S/GUp/70/2023, postanowił:
 I. wyłączyć z masy upadłości:
@@ -637,57 +1590,57 @@
 II. na podstawie art. 357 § 6 k.p.c. w zw. z art. 229 ust. 1 prawa upadłościowego odstąpić od uzasadnienia niniejszego postanowienia wobec uznania w całości zasadności żądania wniosku syndyka i przytoczonych na jego poparcie argumentów przedstawionych szczegółowo w piśmie syndyka z dnia 16 stycznia 2026 roku.</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjE4NmQ5YzItZDM1Ny00OGFiLTgwYmQtMmE0MzRjNGQ4ZTZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>20260407/00067</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>BY1B/GUp-s/107/2026</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>NATALIA</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>MOTYKA</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Markowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>91070515565</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Syndyk masy upadłości w sprawie upadłościowej Natalii Motyki nieprowadzącej działalności gospodarczej w upadłości, sygn. akt: BY1B/GUp-s/107/2026, na podstawie art. 491¹¹a prawa upadłościowego, zawiadamia o wyborze sposobu likwidacji składnika masy upadłości w postaci prawa własności lokalu mieszkalnego nr 18, położonego w Markowicach 43 a o pow. 29,56 m2 dla którego Sąd Rejonowy w Mogilnie prowadzi KW nr BY1M/00020182/3 oraz udziału 1/12 w prawie własności nieruchomości zabudowanej położonej w Markowicach, gmina Strzelno, dz. nr 126/7 o pow.415 m2 objętej KW nr BY1M/00019208/2.
 1.     Syndyk sporządził spis inwentarza oraz przyjął wartość prawa własności lokalu mieszkalnego nr 18, położonego w Markowicach 43 a o pow. 29,56 m2 dla którego Sąd Rejonowy w Mogilnie prowadzi KW nr BY1M/00020182/3, zgodnie z operatem szacunkowym sporządzonym przez rzeczoznawcę majątkowego Pawła Michalskiego w kwocie 107.000,00 zł oraz udziału 1/12 w prawie własności nieruchomości zabudowanej położonej w Markowicach, gmina Strzelno, dz. nr 126/7 o pow.415 m2 objętej KW nr BY1M/00019208/2, zgodnie z operatem szacunkowym sporządzonym przez rzeczoznawcę majątkowego Pawła Michalskiego w kwocie 4.667,00 zł.
@@ -712,57 +1665,57 @@
 9.   W razie odrzucenia skargi sąd z urzędu bierze pod uwagę okoliczności wskazane w skardze i w razie potrzeby wydaje syndykowi polecenie dokonania odpowiednich czynności lub zakazuje syndykowi dokonania określonych czynności.</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNGM0NjA4YmQtMmZmOS00YTFiLWJiMDgtNDFhMmYwMTI4MGQ4JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>20260407/00073</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>WA2M/GUp-s/374/2024</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Anna</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Szkodzińska</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Warszawa, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>00221409523</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>sygn. akt WA2M/GUp-s/374/2024, znak pisma: WA2M/GUp-s/374/2024/167
 Treść obwieszczenia syndyka
@@ -771,49 +1724,49 @@
 nieruchomości: udział 3/8 w prawie własności nieruchomości gruntowej, stanowiącej dz. ew. nr 301 położonej w miejscowości Nuna, gm. Nasielsk, pow. nowodworski, woj. mazowieckie. Dla nieruchomości prowadzona jest księga wieczysta nr OS1U/00037691/4 przez Sąd Rejonowy w Pułtusku, IV Wydział Ksiąg Wieczystych.</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzc1YzliYjQtY2QxNi00ZDY2LTgyMTktOWZmNGEwMjk3MzRhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>20260407/00099</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>GD1G/GUp/90/2023</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
         <is>
           <t>8421775116</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Gdańsk-Północ w Gdańsku</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>VI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 3 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest HIMET SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ SPÓŁKA KOMANDYTOWA, KRS 0000659576, sygnatura akt GD1G/GUp/90/2023, postanowił:
 I. na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego HIMET SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ SPÓŁKA KOMANDYTOWA w postaci:
@@ -825,57 +1778,57 @@
 II. wniosek Syndyka z dn. 30 marca 2026 roku (nr dokumentu: GD1G/GUp/90/2023/78) uczynić integralną częścią niniejszego postanowienia.</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjY4ZmYzNTAtZjIwNi00YzMwLWI0Y2ItMmZkOTA5ZjcwN2ZhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>20260407/00105</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>WA2M/GUp-s/219/2025</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Dariusz</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Pańczyk</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Warszawa, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>71082113535</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>sygn. akt WA2M/GUp-s/219/2025, znak pisma: WA2M/GUp-s/219/2025/51
 Treść obwieszczenia syndyka
@@ -884,65 +1837,65 @@
 nieruchomości: udział 1/2 w prawie własności nieruchomości gruntowej niezabudowanej stanowiącej dz. ew. nr 95/11, obręb 0013, położonej przy ul. Działkowej 20, na terenie miejscowości Warzenko, gmina Przodkowo, powiat kartuski, woj. pomorskiego. Dla nieruchomości prowadzona jest księga wieczysta nr GD1R/00053765/9 przez Sąd Rejonowy w Kartuzach, V Wydział Ksiąg Wieczystych.</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjJiZGRjNTEtZDdkMS00MzFmLTgxNTUtMGMxMDBhZWRiZWZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>20260407/00106</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>ZG1E/GUp-Sędzia-upr/24/2026</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Paulina</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>Urbanowicz-Mróz</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>Zielona Góra, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>88093005320</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Zielonej Górze</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Zielonej Górze, V Wydział Gospodarczy, pl. Słowiański 12, 65-069 Zielona Góra, obwieszcza, że postanowieniem sędziego wyznaczonego z dnia 3 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Paulina Urbanowicz-Mróz (PESEL 88093005320), sygnatura akt ZG1E/GUp-Sędzia-upr/24/2026
 postanowiono:
@@ -951,69 +1904,69 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Zielonej Górze, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMGQ4YzFiMmEtNzY3Ny00NjFmLWJmMGItY2Q5ZDNlOWNmMDYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>20260407/00107</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>PO1P/GUp-Sędzia-upr/1502/2025</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Marcin</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Wdowczyk</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>Poznań, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
         <is>
           <t>83061818753</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>6181937126</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>XI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy, ul. Młyńska 1a, 61-729 Poznań, obwieszcza, że dokumentem z dnia 29 stycznia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Marcin Wdowczyk (PESEL 83061818753), sygnatura akt PO1P/GUp-Sędzia-upr/1502/2025
 obwieszcza: oddalić wniosek pełnomocnika upadłego o wyłączenie z masy upadłości udziałów przysługujących upadłemu w następujących spółkach:
@@ -1022,65 +1975,65 @@
 FORTENZA spółka z ograniczoną odpowiedzialnością, KRS: 0001193113.</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMDA4MmU0MjEtOTQzZi00MTMxLWJmMjQtMTI0ZjQ4NDE1YzQzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>20260407/00150</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>BB1B/GUp-Sędzia-upr/149/2026</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Ewa</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Szczygieł</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Bielsko-Biała, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>55070119686</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Bielsku-Białej</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>VI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Ewa Szczygieł, PESEL 55070119686, prowadzonej pod sygn. akt BB1B/GUp-Sędzia-upr/149/2026,
 postanowił:
@@ -1089,206 +2042,206 @@
 Poucza się, że wierzycielowi przysługuje zażalenie na postanowienie o wyłączeniu z masy upadłości. Zażalenie wnosi się w następujący sposób: wierzyciel może w terminie tygodnia od dnia obwieszczenia postanowienia o wyłączeniu z masy upadłości, wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł. Sąd odrzuci zażalenie jeżeli będzie ono spóźnione, nieopłacone lub dotknięte brakami, które nie zostaną usunięte mimo wezwania. Zażalenie należy skierować do Sądu Upadłościowego - Sądu Rejonowego w Bielsku-Białej, VI Wydział Gospodarczy.</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmI3NjU3MmMtNjc2Ni00NGVjLWEwMzYtN2UwMGZjNTMyMzU5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>20260407/00173</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>KA1K/GUp/16/2023</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Zbigniew</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Nędza</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Czeladź, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
         <is>
           <t>52060202575</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>6251439222</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Katowice Wschód w Katowicach</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>X Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>Syndyk masy upadłości w postępowaniu upadłościowym osoby fizycznej nieprowadzącej działalności gospodarczej Zbigniewa Nędzy PESEL 52060202575, NIP 6251439222 sygn. akt: KA1K/GUp/16/2023, zawiadamia o sporządzeniu opisu i oszacowania przysługującego upadłemu udziału 1/2 w nieruchomości gruntowej zabudowanej w skład której wchodzą działki ewidencyjne nr 5312/227, 5312/341, 5312/478, tworzące całość funkcjonalną o łącznej powierzchni 1104 m2, położonej przy ul. Czarne 13 w Wiśle, dla której Sąd Rejonowy w Cieszynie, V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o numerze BB1C/00089309/1.
 Z treścią opisu i oszacowania uczestnicy postępowania i osoby zainteresowane mogą zapoznać się po uzyskaniu dostępu do akt postępowania w systemie Krajowego Rejestru Zadłużonych. W terminie tygodnia od daty ukazania się niniejszego obwieszczenia można wnieść do sędziego wyznaczonego zarzuty przeciwko opisowi i oszacowaniu. W postępowaniu upadłościowym pisma procesowe oraz dokumenty, z wyłączeniem pism i dokumentów, o których mowa w art. 216ab, wnosi się wyłącznie za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe z wykorzystaniem udostępnianych w tym systemie formularzy. Pisma oraz dokumenty niewniesione za pośrednictwem systemu teleinformatycznego obsługującego postępowanie sądowe nie wywołują skutków prawnych, jakie ustawa wiąże z wniesieniem pisma albo dokumentu do sądu, tymczasowego nadzorcy sądowego, zarządcy przymusowego, syndyka albo organu, do którego przepisy o syndyku stosuje się odpowiednio.</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTk5MTg1OWMtYjNjNC00MWRiLTg2MWMtYzhkMGIwZGVmMTMxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>20260407/00189</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>KI1L/GUp/99/2025</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Mariusz</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>Pietrala</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Kielce, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>68072911392</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>6571000812</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Kielcach</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Sędzia-komisarz w postępowaniu po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza prowadzonym wobec dłużnika, którym jest Mariusz Pietrala (PESEL 68072911392), sygnatura akt KI1L/GUp/99/2025, zarządził:
 o obwieszczeniu, iż syndyk sporządził i przekazał sędziemu-komisarzowi w dniu 3 kwietnia 2026 r. opis i oszacowanie nieruchomości gruntowej położonej w Kielcach przy ul. Skrajnej (dz.ew. nr 504) dla której Sąd Rejonowy w Kielcach VI Wydział Ksiąg Wieczystych prowadzi księgę wieczystą nr KI1L/00051887/0. 
 Zarzuty na opis i oszacowanie wnosi się w terminie tygodnia od dnia obwieszczenia o ich przekazaniu sędziemu-komisarzowi. Zarzuty rozpoznaje sędzia-komisarz.</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzYwY2JhNGMtOGNlYy00M2RkLTllN2MtNTY4MWMwZDQxY2EwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>20260407/00210</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>TR1T/GUp-Sędzia-upr/14/2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Zygmunt</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Sokołowski</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Tarnów, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>58041319052</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>8731168876</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Tarnowie</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Sędzia wyznaczony obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Zygmunt Sokołowski, PESEL 58041319052, sygnatura akt TR1T/GUp-Sędzia-upr/14/2026, postanowił:
 wyłączyć z masy upadłości dłużnika Zygmunta Sokołowskiego składniki majątkowe w postaci:
@@ -1297,61 +2250,61 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Tarnowie, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTY5YWYxODMtOWUwOS00YjZkLTk3MmUtZTM2Zjk3ODVhYjJkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>20260407/00235</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>LU1S/GUp-s/28/2026</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Adam</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>Stawiński</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Matczyn, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>83122403151</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>7132763879</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>sygn. akt LU1S/GUp-s/28/2026, znak pisma: LU1S/GUp-s/28/2026/41
 Treść obwieszczenia syndyka
@@ -1361,138 +2314,138 @@
 Na opis i oszacowanie można wnosić zarzuty w terminie tygodnia od dnia niniejszego obwieszczenia. Zarzuty wnosi się do sędziego-wyznaczonego na adres: Sąd Rejonowy Lublin –Wschód w Lublinie z siedzibą w Świdniku, IX Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych, ul. Kardynała Stefana Wyszyńskiego 18, 21-040 Świdnik.</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTczMmQ1NWEtOThiMi00MzA0LWJjYjgtYTlhZmFhMzUyNWIxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>20260407/00258</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>SW1W/GUp-Sędzia-upr/55/2026</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Mateusz</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Szulc</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>Dzierżoniów, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>90050916275</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>6423134857</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Wałbrzychu</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>VI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Mateusz Szulc, PESEL 90050916275, sygnatura akt SW1W/GUp-Sędzia-upr/55/2026, postanowił:
 wyłączyć z masy upadłości: Ford Transit, nr rejestracyjny PZ 0241Y, rok produkcji 2007, nr VIN WF0XXXTTFX7J73858 .
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Wałbrzychu, VI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M15" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZDBlNjJlMDAtYzlkYy00OTAzLWI4NTctYWNjYmVlN2M0NDUyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>20260407/00269</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>SW1W/GUp-Sędzia-upr/138/2026</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Piotr</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Skowera</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>Wałbrzych, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>83042309135</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>8862589584</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Wałbrzychu</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>VI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Wałbrzychu, VI Wydział Gospodarczy, ul. Juliusza Słowackiego 10,11,11a, 58-300 Wałbrzych, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Piotr Skowera (PESEL 83042309135), sygnatura akt SW1W/GUp-Sędzia-upr/138/2026
 obwieszcza:
@@ -1500,69 +2453,69 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Wałbrzychu, VI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWIzNTk3MzAtYTNhYi00MTY0LWExNjQtZGUxNjI1NjRmNmE2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr">
         <is>
           <t>20260407/00299</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>BY1B/GUp/18/2022</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>TOMASZ</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>GÓRALSKI</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>Inowrocław, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>56102807155</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>5561014019</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Bydgoszczy</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>XV Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest TOMASZ GÓRALSKI, PESEL 56102807155, sygnatura akt BY1B/GUp/18/2022, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia w postaci udziału wynoszącego 1/2 w prawie własności nieruchomości zabudowanej położonej w miejscowości Marcinkowo, gm. Inowrocław:
 a) stanowiącej działkę nr 58/6, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00027957/2, za cenę nie niższą niż 40% wartości oszacowania, tj. 232 400 (dwieście trzydzieści dwa tysiące czterysta) złotych,
@@ -1571,332 +2524,332 @@
 d) stanowiącej działkę nr 58/8, dla której Sąd Rejonowy w Inowrocławiu prowadzi księgę wieczystą KW nr BY1I/00057358/2, za cenę nie niższą niż 40% wartości oszacowania, tj. 149 200 (sto czterdzieści dziewięć tysięcy dwieście) złotych.</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNWY0ZTgzMWEtNjIxNy00ZjhiLWE3MTMtNjBkN2IwNzlhNGFhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>20260407/00337</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>OL1O/GUp-Sędzia-upr/143/2026</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Jacek</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Czechowski</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>Szczytno, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>53091201573</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>7450002600</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Olsztynie</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Jacek Czechowski, PESEL 53091201573, sygnatura akt OL1O/GUp-Sędzia-upr/143/2026, postanowił:
 wyłączyć z masy upadłości udziały członkowskie upadłego w Banku Spółdzielczym w Szczytnie w wysokości 200 zł.
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Olsztynie, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMzdjNWI0NDUtMmYzNC00ZWU1LWFmOWQtYjhmODhiYjllOTFhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t>20260407/00397</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>KI1L/GUp/29/2024</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Sławomir</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Michalec</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>Kielce, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>63042609855</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>9590217508</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Kielcach</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Sędzia-komisarz w postępowaniu po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza prowadzonym wobec dłużnika, którym jest Sławomir Michalec (PESEL 63042609855), sygnatura akt KI1L/GUp/29/2024, zarządził:
 o obwieszczeniu, iż syndyk sporządził i przekazał sędziemu-komisarzowi w dniu 2 kwietnia 2026 r. opis i oszacowanie udziału wynoszącego 1/2 w prawie współwłasności nieruchomości lokalowej nr 11, przy ul. Karbońskiej 4 w Kielcach.
 Zarzuty na opis i oszacowanie wnosi się w terminie tygodnia od dnia obwieszczenia o ich przekazaniu sędziemu-komisarzowi. Zarzuty rozpoznaje sędzia-komisarz.</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNTY4M2NiMGQtZGVjYi00NWFjLWIzYmEtNDg0OWY4NmYyMTMzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="35">
+      <c r="A35" t="inlineStr">
         <is>
           <t>20260407/00400</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>OP1O/GUp-Sędzia-upr/21/2026</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>OLGA</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>KUBICA</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>Dytmarów, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>87062316609</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Opolu</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Sędzia wyznaczony obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest OLGA KUBICA, PESEL 87062316609, prowadzonej pod sygn. akt OP1O/GUp-Sędzia-upr/21/2026, postanowił:
 na podstawie art. 63 ust. 1 pkt 1 w zw. z art. 4912 ust. 1 ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe w zw. z art. 829 pkt 6 k.p.c. stwierdzić, że samochód osobowy marki Volkswagen Turan, numer rejestracyjny OPR6F7, rok produkcji 2010, ujawniony w spisie inwentarza pod numerem 1.1 nie wchodzi w skład masy upadłości.
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Opolu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYWIwZGIzZDAtZDQwYS00MWVkLTkzMGMtYzA1MzE3YTExNTJlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="36">
+      <c r="A36" t="inlineStr">
         <is>
           <t>20260407/00425</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>ZG1E/GUp-s/2/2026</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>Tomasz</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Szymański</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>Czerwieńsk, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>76010604019</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>9730245078</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Informuje się, że w postępowaniu upadłościowym upadłego, którym jest Tomasz Szymański PESEL 76010604019, prowadzonego pod sygn. akt: ZG1E/GUp-s/2/2026 złożono do akt opis i oszacowanie prawa własności nieruchomości gruntowej niezabudowanej, położonej w Nietkowie, gmina Czerwieńsk, województwo lubuskie, oznaczonej jako działka nr 963/2, dla której prowadzona jest księga wieczysta ZG1E/00099879/8 oraz prawa własności nieruchomości gruntowej niezabudowanej, położonej w Nietkowie, gmina Czerwieńsk, województwo lubuskie, oznaczonej jako działka nr 347/5, dla której prowadzona jest księga wieczysta ZG1E/00008006/4.
 Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNmY2NGQ3MDctY2E3ZS00YjI4LWJjNDUtYjhmNGQxOTcyYjYxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>20260407/00440</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>WA2M/GUp/1/2025</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>Daniel</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Jabłoński</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>Warszawa, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>85021600116</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>7010012994</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>XIX Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Daniel Jabłoński, PESEL 85021600116, sygnatura akt WA2M/GUp/1/2025, postanowił:
 na podstawie art. 4911 ust. 2 w zw. art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego, którym jest Daniel Jabłoński, w postaci należności od Lazzoni Group sp. z o.o. sp.k. (składnik masy upadłości w spisie inwentarza numer 5.1 oraz w uzupełniającym spisie inwentarza nr 5.3) przysługującej solidarnie również Rafałowi Grucy, wobec którego toczy się postępowania upadłościowe pod sygnaturą WA2M/GUp/2/2025, o wartości nominalnej 85.000 zł za 50% ceny wynikającej z oszacowania (wartość rynkowa na podstawie Oszacowania z dnia 20 marca 2026 r. sporządzonego przez biegłego sądowego Wojciecha Makucia, dołączonej do akt postępowania upadłościowego pod nr 147, znak w aktach WA2M/GUp/2/2025/147) , czyli:
@@ -1904,61 +2857,61 @@
 2.   za cenę nie niższą niż 2.346,00 zł (dwa tysiące trzysta czterdzieści sześć złotych) netto, w przypadku gdyby aukcja przeprowadzona w terminie wskazanym w pkt 1, nie doszła do skutku ze względu na brak oferentów, jak również ustalenie, że syndyk przeprowadzi aukcję po obniżonej cenie, podaną do publicznej wiadomości, w terminie nie wcześniejszym niż po upływie dwóch tygodni od upływu terminu przeprowadzenia aukcji wskazanego w pkt 1;</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjllNjJlNDYtMzYzMi00MTNjLWFhMTYtOTBmZGYzNzM2YmI2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>20260407/00456</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>BY1B/GUp-s/419/2025</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>MAGDALENA</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>KRAJEWSKA</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>Niszczewice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>76061002002</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>5562409843</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Syndyk, którym jest Maciej Grzelak, obwieszcza, że dokumentem z dnia 31 marca 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest MAGDALENA KRAJEWSKA (PESEL 76061002002), sygnatura akt BY1B/GUp-s/419/2025
 obwieszcza:
@@ -2015,65 +2968,65 @@
 6. Złożenie oferty jest równoznaczne z akceptacją niniejszego regulaminu oraz treści ogłoszenia.</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZDZiOThiZjQtMzZlNy00OGE0LWIxNTItZGQ5MTg5M2U4OGMzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>20260407/00481</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>BB1B/GUp-Sędzia-upr/28/2026</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Danuta</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Wiercigroch</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>Bielsko-Biała, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>56122111469</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Bielsku-Białej</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>VI Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Sąd Rejonowy w Bielsku-Białej, VI Wydział Gospodarczy, ul. Wojciecha Bogusławskiego 24, 43-300 Bielsko-Biała, obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Danuta Wiercigroch (PESEL 56122111469), sygnatura akt BB1B/GUp-Sędzia-upr/28/2026
 postanowił:
@@ -2082,69 +3035,69 @@
 Poucza się, że wierzycielowi przysługuje zażalenie na postanowienie o wyłączeniu z masy upadłości. Zażalenie wnosi się w następujący sposób: wierzyciel może w terminie tygodnia od dnia obwieszczenia postanowienia o wyłączeniu z masy upadłości, wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł. Sąd odrzuci zażalenie jeżeli będzie ono spóźnione, nieopłacone lub dotknięte brakami, które nie zostaną usunięte mimo wezwania. Zażalenie należy skierować do Sądu Upadłościowego - Sądu Rejonowego w Bielsku-Białej, VI Wydział Gospodarczy.</t>
         </is>
       </c>
-      <c r="M24" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWJhYjEzNDEtYjhiZC00ZjE0LWI2MjUtZjQ4YjMxYTA2NGI2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>20260407/00500</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>07.04.2026</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>WA2M/GUp-Sędzia-upr/443/2025</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Adam</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Jabłonka</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>Warszawa, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>87061208992</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>7822346886</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>XIX Wydział Gospodarczy</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie, XIX Wydział Gospodarczy, ul. Czerniakowska 100a, 00-454 Warszawa, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Adam Jabłonka (PESEL 87061208992), sygnatura akt WA2M/GUp-Sędzia-upr/443/2025
 postanowił:
@@ -2153,297 +3106,2639 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego dla m.st. Warszawy w Warszawie, XIX Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyM2ZmYWUzZmMtMmRkZC00YjY1LThjNzMtMzQzMjRmNTk1ZjdkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20260407/00523</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>KI1L/GUp/100/2025</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MONIKA</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>HAAS</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Ożarów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>74110809581</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Kielcach</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest MONIKA HAAS, PESEL 74110809581, sygnatura akt KI1L/GUp/100/2025, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości upadłego, którym jest MONIKA HAAS w postaci nieruchomości położonej w miejscowości Sobótka, gm. Ożarów, składającej się z działki gruntu o numerze ewidencyjnym 256/2 o pow. 0,1955ha, zabudowanej budynkiem mieszkalnym o powierzchni użytkowej 79,36m2 oraz budynkiem gospodarczym o powierzchni 45,08m2, dla której Sąd Rejonowy w Sandomierzu V Wydział Ksiąg Wieczystych prowadzi nr KI1S/00074179/7, za cenę nie niższą niż 157 870 ,50 zł. zgodnie z regulaminem stanowiącym załącznik do wniosku.
+Na niniejsze orzeczenie nie przysługuje zażalenie.</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMTJiMDhmNTQtODE0My00MTBiLTg3MzAtNDhhMzQzYzgyYWRjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20260407/00541</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LD1M/GUp/48/2025</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Monika</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Majchrzak</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Konstantynów Łódzki, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>89062511022</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>7311968888</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Łodzi-Śródmieścia w Łodzi</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>XIV Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz w postępowaniu po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza prowadzonym wobec dłużnika, którym jest Monika Majchrzak (numer PESEL 89062511022), sygnatura akt LD1M/GUp/48/2025, zarządził:
+obwieścić o sporządzeniu i przekazaniu sędziemu-komisarzowi 7 kwietnia 2026 roku opisu i oszacowania należącego do upadłej udziału w prawie własności nieruchomości gruntowej, położonej we wsi Magnusy w Gminie Wodzierady, w powiecie łaskim, w województwie łódzkim, oznaczonej w ewidencji gruntów numerem działki 324, w obrębie 0015 Magnusy, dla której Sad Rejonowy w Łasku V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o numerze SR1L/00069497/9.
+Opis i oszacowanie jest dostępny w aktach sprawy prowadzonych w systemie teleinformatycznym obsługującym postępowanie sądowe (Krajowy Rejestr Zadłużonych) pod sygnaturą akt LD1M/GUp/48/2025.
+Na opis i oszacowanie można wnieść zarzuty w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia - za pośrednictwem systemu teleinformatycznego (Krajowy Rejestr Zadłużonych) do sędziego-komisarza - Sąd Rejonowy dla Łodzi-Śródmieścia w Łodzi XIV Wydział Gospodarczy dla spraw Upadłościowych i Restrukturyzacyjnych – z podaniem sygnatury akt LD1M/GUp/48/2025.</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMTc4NzAyYmItOWZlMi00NDYwLWFmMzItYjkwZjVkZTg1MjcwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20260407/00556</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-s/1543/2025</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Alfred</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Smolarek</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Międzylesie, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>63020810495</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>sygn. akt PO1P/GUp-s/1543/2025, znak pisma: PO1P/GUp-s/1543/2025/24
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Alfred Smolarek, prowadzonego pod sygn. akt: PO1P/GUp-s/1543/2025, złożono do akt opis i szacowanie:
+nieruchomości: 1) nieruchomości gruntowej położonej w Międzylesiu, Kw PO1O/00024833/5 o pow. 7,4400 ha. sposób użytkowania: rola, sad, budynki, nieużytki, pastwisko, łąka las, woda, budynek mieszkalny i budynki gosp. o wartości łącznej 701 200 zł z czego udział upadłego wynosi 66.780,95 zł. 2) nieruchomości gruntowej KW PO1O/00026387/7 położonej w Międzylesiu, sposób użytkowania: rola o pow. 2,6700 ha o łącznej wartości 133 400 zł z czego udział upadłego wynosi 12.704,76 zł.</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMGE2YzllOWUtMmQ2ZC00OTc0LWExODEtMTY3Y2ZjZTY2NGU4JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20260407/00559</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TR1T/GUp-Sąd-upr/82/2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Halina</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Podlasek</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tarnów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>68050607585</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Tarnowie</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Tarnowie, V Wydział Gospodarczy, ul. Dąbrowskiego 27, 33-100 Tarnów, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sąd w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Halina Podlasek (PESEL 68050607585), sygnatura akt TR1T/GUp-Sąd-upr/82/2026
+obwieszcza: oddalono - na zasadzie art. 4912 ust. 2 p.u. - wniosek syndyka o zmianę sposobu prowadzenia postępowania upadłościowego.
+Na postanowienie nie przysługuje środek zaskarżenia.</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzlmY2Y1ZDUtNTFjNC00YzNjLTgwYmYtNDAwN2JmYTExMDNjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20260407/00578</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OP1O/GUp-Sędzia-upr/59/2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Piotr</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Owczarek</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Domaszowice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>51062802790</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7520000754</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Opolu</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Sędzia wyznaczony w Sądzie Rejonowym w Opolu V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Piotr Owczarek, PESEL 51062802790, prowadzonej pod sygn. akt OP1O/GUp-Sędzia-upr/59/2026, w przedmiocie wniosku upadłego o ograniczenie potrąceń do masy upadłości postanowił:
+oddalić wniosek.
+------
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Opolu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Opolu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie wnosi się w następujący sposób w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze należy złożyć wniosek o sporządzenie uzasadnienia i doręczenie odpisu postanowienia wraz z pisemnym uzasadnieniem. We wniosku należy wskazać, czy pisemne uzasadnienie ma dotyczyć całości postanowienia czy jego części, w szczególności poszczególnych objętych nim rozstrzygnięć. Wniosek o doręczenie odpisu postanowienia wraz z pisemnym uzasadnieniem podlega opłacie w wysokości 100,00 zł. Sąd odrzuci wniosek o doręczenie odpisu postanowienia z pisemnym uzasadnieniem, jeżeli będzie on spóźniony, nieopłacony lub dotknięty brakami, które nie zostaną usunięte mimo wezwania. Po doręczeniu odpisu postanowienia wraz z uzasadnieniem na piśmie należy w ciągu tygodnia wnieść zażalenie. Zażalenie podlega opłacie w wysokości 200,00 zł, przy czym uiszczona już opłata 100,00 zł za sporządzenie uzasadnienia zaliczona zostanie na poczet opłaty od zażalenia. Zażalenie może być wniesione tylko co do tej części postanowienia, co do której zażądano uzasadnienia.</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYzA2NTBmZjgtM2M4YS00NzM2LTg4ZDMtNGNmYTAxZjc4YTFjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>20260407/00593</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp/84/2024</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>8551584308</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Szczecin-Centrum w Szczecinie</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>XII Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest VIKING YARD Spółka z ograniczoną odpowiedzialnością z siedzibą w Świnoujściu(KRS 0000528740), sygnatura akt SZ1S/GUp/84/2024, postanowił:
+zezwolić syndykowi masy upadłości na zawarcie ugody pozasądowej co do roszczenia przysługującego upadłemu, którym jest VIKING YARD Spółka z ograniczoną odpowiedzialnością z siedzibą w Świnoujściu, wobec podmiotu, którym jest Paweł Gorzkowicz, wynikającego z prawomocnego wyroku Sądu Rejonowego w Świnoujściu I Wydziału Cywilnego z dnia 27 listopada 2025 r., wydanego pod sygn. akt I C 446/25, na następujących warunkach:
+1) spłata należności głównej przez Pawła Gorzkowicza nastąpi w siedmiu równych, miesięcznych ratach, w terminie do 10. dnia każdego miesiąca, przelewem na rachunek bankowy masy upadłości, przy czym za dzień zapłaty uznany będzie dzień zasilenia rachunku masy upadłości,
+2) spłata odsetek przez Pawła Gorzkowicza nastąpi w ramach raty ósmej, w terminie do 10. dnia miesiąca następującego po ostatnim miesiącu spłaty należności głównej, przelewem na rachunek bankowy masy upadłości, przy czym za dzień zapłaty uznany będzie dzień zasilenia rachunku masy upadłości,
+3) syndyk masy upadłości zostanie zwolniony z obowiązku zapłaty na rzecz Pawła Gorzkowicza kwoty 540,00 zł zasądzonej w punkcie III wyroku,
+4) w przypadku uchybienia przez Pawła Gorzkowicza terminowi zapłaty którejkolwiek z rat, postanowienia ugody dotyczące rozłożenia na raty wygasną, powodując wymagalność zobowiązania w niezaspokojonej części i możliwość dochodzenia (egzekucji) roszczenia na zasadach ogólnych,
+5) ugoda zostanie zawarta w terminie nie dłuższym niż siedem dni od dnia wydania niniejszego postanowienia.
+Pouczenie:
+Postanowienie jest niezaskarżalne.</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYzM3ZGJjMDQtYTlkZS00YmZhLWEwYzAtYzM2NzViYWFkYjFlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>20260407/00600</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RA1R/GUp-Sędzia-upr/45/2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Albert</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Pszczoła</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kozienice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>78011802472</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Radomiu</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Albert Pszczoła, PESEL 78011802472, sygnatura akt RA1R/GUp-Sędzia-upr/45/2026, postanowił:
+wyłączyć z masy upadłości składnik majątku w postaci 200 udziałów o wartości 500 zł każdy udział o łącznej wartości nominalnej 100 000 zł, przysługujących Upadłemu w T&amp;T PEOPLE WORK CIBUS Spółce z ograniczoną odpowiedzialnością z siedzibą w Krakowie (KRS: 0000812798);
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Radomiu, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWY2MzVlOWQtZGZiMy00OWY5LWFjNGUtOWQ2MWFkMTRhMDUzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>20260407/00616</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-s/1097/2024</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>EDYTA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>KIERDELEWICZ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Poznań, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>79010411863</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7831745108</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Agnieszka Fuglewicz, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest EDYTA KIERDELEWICZ (PESEL 79010411863), sygnatura akt PO1P/GUp-s/1097/2024
+REGULAMIN
+ Syndyk masy upadłości Edyty Kierdelewicz – Agnieszka Fuglewicz sprzeda z wolnej ręki majątek wchodzący w skład masy upadłości Upadłej Edyty Kierdelewicz osoby fizycznej nieprowadzącej działalności gospodarczej na następujących warunkach: 
+ 1.       Przedmiotem sprzedaży jest ½ części spółdzielczego własnościowego prawa do lokalu mieszkalnego nr 14, położonego w Białymstoku przy ul. Ślusarskiej 16, dla którego prowadzona jest księga wieczysta nr BI1B/00206416/1. Cena wywoławcza wynosi 127 400,00 zł.
+2.      Sprzedaż w/w prawa następuje na podstawie ustawy z dnia 28 lutego 2003 roku Prawo upadłościowe (dalej jako PU), oraz Kodeksu Cywilnego. 
+3.      Sprzedaż może nastąpić za cenę nie niższą niż wskazana wyżej cena wywoławcza. 
+4.     Szczegółowy opis przedmiotu sprzedaży będzie udostępniony przez syndyka masy upadłości w odpowiedzi na zapytanie oferenta.
+5.      Sprzedaż nastąpi na rzecz oferenta oferującego najwyższą cenę, za cenę nie niższą niż cena minimalna. 
+6.      W postępowaniu na sprzedaż nie mogą uczestniczyć: upadły, syndyk, jego małżonek, dzieci oraz obecni podczas rozpatrywania ofert w charakterze urzędowym. W pozostałym zakresie krąg oferentów jest nieograniczony podmiotowo. 
+7.      Oferta winna zawierać: - oznaczenie oferenta, proponowaną cenę nabycia, podpis oferenta lub upoważnionej przez oferenta osoby działającej w jego imieniu, nr telefonu, adres e-mailowy, - oryginał lub uwierzytelnioną notarialnie kserokopię zaświadczenia o wpisie do właściwego Rejestru Przedsiębiorców albo poświadczoną notarialnie kserokopię dowodu osobistego, jeżeli oferentem jest osoba fizyczna, - oryginał lub uwierzytelnioną notarialnie kserokopię decyzji właściwego Urzędu Skarbowego o nadaniu numeru identyfikacji podatkowej (NIP), - oryginał lub uwierzytelnioną notarialnie kserokopię zaświadczenia o numerze identyfikacyjnym REGON wydanym przez właściwy Urząd Statystyczny, - oryginał ewentualnie udzielonego pełnomocnictwa albo jego kserokopię potwierdzoną za zgodność z oryginałem przez notariusza, - oświadczenie o wyrażeniu zgody na pokrycie wszelkich kosztów związanych z przeniesieniem własności, - oświadczenie o zapoznaniu się ze stanem przedmiotu postępowania w tym prawnym i technicznym oraz oświadczenie o wyrażeniu zgody na wyłączenie rękojmi za wady fizyczne i prawne na zasadzie art. 558 kc, - oświadczenie, że oferent nie należy do grona osób określonych w pkt 6 niniejszych warunków postępowania, potwierdzenie wpłaty wadium na zakup nieruchomości gruntowej niezabudowanej, będącej przedmiotem składanej oferty, tj. 5% ceny oszacowania, tj. 6370,00 zł.
+8.     Oferta nie zawierająca chociażby jednego z elementów określonych w pkt 7, złożona z przekroczeniem terminu lub z uchybieniem obowiązku wpłaty wadium nie będzie podlegała rozpatrzeniu. 
+9.      Oferty w języku polskim lub w tłumaczeniu na język polski przez przysięgłego tłumacza w zaklejonych kopertach uniemożliwiających ich otwarcie z wyraźnym i czytelnym oznaczeniem oferenta, a także z dopiskiem „Postępowanie sprzedaży nieruchomości – Edyta Kierdelewicz” przesyłając pocztą na adres biura Syndyka: Kancelaria Radcy Prawnego Agnieszka Fuglewicz ul. Nad Potokiem 17/4, 60-639 Poznań składać należy do dnia 8.05.2026 roku. Liczy się data wpływu. 
+10.    Składający ofertę na nabycie przedmiotu postępowania powinien pod rygorem nierozpoznania oferty przez syndyka wpłacić na rachunek bankowy masy upadłości o numerze: 42 2490 0005 0000 4100 5850 3719 wadium w wysokości 5% ceny oszacowania. Złożenie chociażby jednej oferty wystarcza do odbycia postępowania na sprzedaż ww. składnika majątku. 
+11.Syndyk dokona protokolarnego otwarcia ofert w biurze syndyka.
+12. Syndyk wybiera najbardziej korzystną z ofert bądź ustala, że żadna z ofert nie została przyjęta.
+13. P
+rzy wyborze oferty Syndyk kieruje się wysokością zaoferowanej ceny i warunkami jej płatności.
+14.Z prz
+eprowadzonych czynności Syndyk sporządza protokół, podając w nim rozstrzygnięcie przetargu.
+15.Syndyk ni
+ezwłocznie zawiadamia oferenta o wyborze jego oferty i warunkach dokonania sprzedaży oraz o terminie zawarcia umowy sprzedaży.
+16.W przypadk
+u braku ofert Syndyk może przeprowadzić kolejny przetarg na nowych warunkach sprzedaży.
+17.Z dniem zawa
+rcia umowy sprzedaży na nabywcę przechodzą:
+a)     pożytki,
+jakie przynosi przedmiot sprzedaż
+y,
+b)     obowiązki
+w zakresie podatków i ubezpieczeń związanych z przedmiotem sprzed
+aży.
+18.Sprzedawca nie jest
+odpowiedzialny względem kupującego z tytułu rękojmi za wady lub braki sprzedawanej nieruchomości, ponadto Kupującemu nie przysługuje prawo zwrotu zakupionej nieruchomości, na co Kupujący wyraża zgodę.
+19.    W przypadku, gdyby o
+ferty złożone obejmowały tę samą cenę ofertową na przedmiot sprzedaży przewiduje się możliwość przeprowadzenia ustnej licytacji celem wyłonienia oferenta, z kwotą postąpienia 1 000,00 złotych. 
+ 20.    Syndyk zobligowany
+jest do podpisania umowy sprzedaży z oferentem w terminie do sześciu miesięcy od daty wyboru oferty. 
+21.    Cena sprzedaży win
+na być zapłacona w całości najpóźniej do dnia zawarcia umowy sprzedaży - przed jej zawarciem. Przeniesienie na własność oferowanego składnika majątku nastąpi po zapłacie całej ceny przez oferenta. 
+22.    Wadium złożone pr
+zez oferenta, którego oferta została wybrana przez syndyka, zostanie zaliczone na poczet ceny nabycia. Pozostałym oferentom, wadium zostanie zwrócone bez odsetek i oprocentowania w terminie 7 dni od daty wyboru ofert. 
+23.    Jeżeli nabywca n
+ie wykona ze swej winy warunków oferty w terminie sześciu miesięcy od dnia wyboru jego oferty przez syndyka, traci wadium i zostaje wykluczony z postępowania. 
+24.    Koszty sprawdze
+nia przedmiotu sprzedaży i zawarcia umowy sprzedaży w miejscu wskazanym przez syndyka ponosi kupujący. 
+25.   Zastrzega się m
+ożliwość odwołania w całości lub w części postępowania lub też jego unieważnienia na każdym etapie bez podania przyczyny. 
+26.Wszelkich informa
+cji udziela Syndyk masy upadłości Edyty Kierdelewicz – Agnieszka Fuglewicz e-mail: fuglewicz.kancelaria@gmail.com</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTU5NGIxNjAtMTk5NC00YWJlLTgwMTMtOTU0ZGM2ZTkwYWYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>20260407/00647</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LE1L/GUp-Sędzia-upr/39/2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Małgorzata</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Sadłocha</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kotla, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>88090809606</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Legnicy</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Legnicy, V Wydział Gospodarczy, ul. Złotoryjska 19, 59-220 Legnica, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Małgorzata Sadłocha (PESEL 88090809606), sygnatura akt LE1L/GUp-Sędzia-upr/39/2026
+obwieszcza: I.                   umorzyć postępowanie w przedmiocie wniosku upadłej o określenie, że w skład masy upadłości nie wchodzi wierzytelność z tytułu nadpłaty podatku dochodowego za rok 2025 do wysokości kwoty 2.000,00 zł,
+II.                określić, że do masy upadłości nie będzie wchodzić dochód upadłej z tytułu zapomogi przyznanej przez pracodawcę z Zakładowego Funduszu Świadczeń Socjalnych w dniu 12 marca 2026 r. w wysokości 8 000,00 zł w związku ze zdarzeniem losowym.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Legnicy, V Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTM2N2NmMTMtMTljZS00MTU2LTgyZjMtYWU3NGZmMmFkNzUyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>20260407/00650</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>BY1B/GUp/11/2023</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5542985609</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bydgoszczy</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>XV Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest PLAST-COM.PL Spółka z ograniczoną odpowiedzialnością, KRS 0000842768, sygnatura akt BY1B/GUp/11/2023, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia w postaci ruchomości stanowiącej wózek widłowy HC CPQD25N-RW52-Y (poz. 1.164 uzupełniającego spisu inwentarza) za cenę nie niższą niż cena oszacowania, tj. nie niższą niż 34 500 zł (trzydzieści cztery tysiące pięćset złotych).</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYzhmYzJkZDMtZGYxMS00MDI1LWExNzQtODI2YmM0MjhlMzljJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>20260407/00670</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PL1P/GUp-Sędzia-upr/137/2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Grodecki</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Rościszewo, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>80041712672</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7761502888</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Płocku</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Mariusz Grodecki, PESEL 80041712672, prowadzonej pod sygn. akt PL1P/GUp-Sędzia-upr/137/2026, w przedmiocie wniosku upadłego o wyłączenie z masy upadłości samochodu osobowego marki Opel Astra, nr rej. WSE 4SV5, numer VIN WOLOAHL35D2018259, postanowił:
+oddalić wniosek.
+Postanowienie zostało wydane na posiedzeniu niejawnym z uzasadnieniem. Na postanowienie upadłemu i wierzycielom przysługuje zażalenie do sądu upadłościowego - Sądu Rejonowego w Płocku, V Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyM2MwNDJkNGQtM2IyMy00M2U4LWJjZTEtZDg5MGRhNDViN2YwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>20260407/00671</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BY1B/GUp/11/2023</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5542985609</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Bydgoszczy</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>XV Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest PLAST-COM.PL Spółka z ograniczoną odpowiedzialnością, KRS 0000842768, sygnatura akt BY1B/GUp/11/2023, postanowił: na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia w postaci ruchomości wskazanych w załączniku do wniosku syndyka z dnia 13 marca 2026 r. (znak w aktach BY1B/GUp/11/2023/243) za ceny nie niższe niż ceny wskazane w kolumnie nr 8 dołączonego załącznika.</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNjY3YzhmYTYtY2JiZi00ZmU3LThkMTEtOTY1NjBhNjk5MmNiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>20260407/00685</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>KI1L/GUp/108/2025</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Ewa</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ptak</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Kielce, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>64061302406</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>6571742465</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Kielcach</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Ewa Ptak, PESEL 64061302406, sygnatura akt KI1L/GUp/108/2025, postanowił:
+na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki wchodzącego w skład masy upadłości mienia w postaci spółdzielczego własnościowego prawa do lokalu mieszkalnego - lokalu mieszkalnego nr 68 położonego w Kielcach przy ul. Barwinek 15, o powierzchni użytkowej 70,64 m2, dla którego to prawa Sąd Rejonowy w Kielcach, VI Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o numerze KI1L/00134607/0;
+2. określić syndykowi masy upadłości upadłego Ewy Ptak następujące warunki sprzedaży z wolnej ręki wyżej opisanego prawa:
+a). zbycie przez syndyka masy upadłości nieruchomości opisanej w pkt. 1 nie może nastąpić za cenę niższą niż 75% ceny oszacowania tj. za kwotę 418 680,00 zł (słownie: czterysta osiemnaście tysięcy sześćset osiemdziesiąt złotych 00/100) Jeżeli sprzedaż udziału podlega opodatkowaniu, do ceny zostanie doliczony stosowny podatek;
+b). osoby zainteresowane nabyciem nieruchomości winny składać oferty bezpośrednio w Kancelarii syndyka;
+c). sprzedaż zostanie poprzedzona ogłoszeniami w przynajmniej dwóch popularnych portalach internetowych zajmujących się sprzedażą nieruchomości;
+d). zawarcie umowy sprzedaży z oferentem będzie możliwe nie wcześniej niż po upływie 14 dni od dnia ukazania się późniejszego chronologicznie ogłoszenia na portalu internetowym;
+e). syndyk w sytuacji złożenia ofert przez kilku oferentów przeprowadzi w celu uzyskania najwyższej ceny aukcję pomiędzy oferentami;
+f). zawarcie umowy sprzedaży możliwe będzie po uprzednim uiszczeniu przez oferenta całości ceny na rachunek bankowy syndyka masy upadłości;
+g). koszty zawarcia umowy sprzedaży ponosi w całości kupujący.
+Postanowienie jest prawomocne.</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNmZlNWNkOTktMWZjMS00NGI0LTk2MTMtNWI5MDQ5MGUzN2VjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>20260407/00696</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>WR1F/GUp-s/82/2025</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ewelina</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Milik</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Kostomłoty, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>83101811463</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9131521968</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Działając jako syndyk masy upadłości Eweliny Milik osoby fizycznej nieprowadzącej działalności gospodarczej, zgodnie z brzmieniem art. 49111a ust. 2 PU zawiadamiam, iż planowane jest spieniężenie składnika masy upadłości w postaci wierzytelności w kwocie 23.825,10 zł jako należność główna wraz z odsetkami liczonymi od dnia 9 października 2023 r. do dnia zapłaty oraz kosztami procesu w kwocie 1192 zł w stosunku do HyggeGo sp. z o.o. wynikającą z nakazu zapłaty w postępowaniu upominawczym Sądu Rejonowego w Siedlcach Wydział V Gospodarczy sygn. akt V GNc 1051/25 za cenę obniżoną, nie mniejszą niż 1191,25 zł stanowiącą 5 % z należności głównej. Syndyk wybiera formę sprzedaży w trybie sprzedaży z wolnej ręki. Przyczyną obniżki jest fakt, że dotychczasowy oferent wycofał swoją ofertę, a żadna inna nie wpłynęła.</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNjdlZTI2NDMtYjY3My00Y2QyLWJkYjAtMDg4NTg5MDU1ZTlhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>20260407/00707</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>WR1F/GUp/2/2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sylwia</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Iwanicka</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Oława, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>76121610783</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Wrocławia-Fabrycznej we Wrocławiu</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>VIII Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Sylwia Iwanicka , PESEL 76121610783, sygnatura akt WR1F/GUp/2/2026, postanowił:
+I. w trybie art. 315 Prawa upadłościowego wyłączyć z masy upadłości samochód osobowy Seat Leon (nr rej. DOA77412; poz. 1.1 spisu inwentarza);
+II. na postawie art. 229 Prawa upadłościowego w zw. z art. 357 § 6 k.p.c. odstąpić od uzasadnienia niniejszego postanowienia, którym Sędzia-komisarz w całości uwzględnił wniosek upadłej, złożony 2.03.2026 r. (dok. nr 21) podzielając argumenty przytoczone przez dłużnika na jego poparcie.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego dla Wrocławia-Fabrycznej we Wrocławiu, VIII Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.
+Zażalenie powinno czynić zadość wymaganiom przepisanym dla pisma procesowego oraz zawierać wskazanie zaskarżonego orzeczenia i wniosek o jego zmianę lub uchylenie, jak również zwięzłe uzasadnienie ze wskazaniem w miarę potrzeby nowych faktów i dowodów.
+Sąd odrzuci zażalenie, jeżeli będzie ono spóźnione, nieopłacone lub dotknięte brakami, które nie zostaną usunięte mimo wezwania.</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjI0NzIxMmEtNjlmNS00Mzc0LWE2ZWItNjdlNGNjZWNkOTUxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>20260407/00713</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ZG1E/GUp-s/242/2023</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Tomasz</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Strzeszewski</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Małaszowice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>84030806319</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>9251945978</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>sygn. akt ZG1E/GUp-s/242/2023, znak pisma: ZG1E/GUp-s/242/2023/41
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Tomasz Strzeszewski, prowadzonego pod sygn. akt: ZG1E/GUp-s/242/2023, złożono do akt opis i szacowanie nieruchomości: nieruchomości gruntowej położona w miejscowości Małaszowice, gmina Bytom Odrzański o powierzchni 1.228 m2, nr działki 120/4, dla której Sąd Rejonowy w Nowej Soli V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o nr ZG1N/00073942/2.
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyODg2MzNlOGUtYzAyNS00NjkyLTg4ZjAtY2Y2YTE5YThkOGI3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>20260407/00717</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/67/2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Szymański</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Warzymice, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>91032215018</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>6922473106</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Elżbieta Ahl, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Mariusz Szymański (PESEL 91032215018), sygnatura akt SZ1S/GUp-s/67/2026
+obwieszcza: iż w dniu 07.04.2026r. do akt postępowania złożono spis inwentarza oraz plan likwidacyjny z preliminarzem wydatków.</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNmMzMWE4MjYtYjU4MC00ODdjLThmOWEtMzI3MjgxODQ3YTZiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>20260407/00727</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>WA2M/GUp-s/420/2025</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Agnieszka</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Kocoń</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Warszawa, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>78011209644</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5321593472</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>sygn. akt WA2M/GUp-s/420/2025, znak pisma: WA2M/GUp-s/420/2025/75
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Agnieszka Kocoń, prowadzonego pod sygn. akt: WA2M/GUp-s/420/2025, złożono do akt opis i szacowanie:
+nieruchomości: położonej w Celejowie, gmina Wilga, powiat garwoliński, województwo mazowieckie, obręb 0001 Celejów, składająca się z działek ewidencyjnych nr 1/5 i 1/6 dla której Sąd Rejonowy w Garwolinie prowadzi księgę wieczystą o numerze SI1G/00081346/7 wraz z posadowionym na niej budynkiem; nieruchomość położona w położonej w Celejowie, gmina Wilga, powiat garwoliński, województwo mazowieckie, obręb 0001 Celejów, składająca się z działek ewidencyjnych nr 1/3, dla której Sąd Rejonowy w Garwolinie prowadzi księgę wieczystą o numerze SI1G/00046170/5.
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNDZjYWFjOGMtZDI2OS00NDdmLWI0MGQtMzVhZjQwOTVjNDRmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>20260407/00783</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>WA1M/GUp/9/2025</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>6612372285</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla m.st.Warszawy w Warszawie</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>XVIII Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 25 marca 2026 roku wydanym w sprawie po ogłoszeniu upadłości upadłego, którym jest N13 SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ Spółka z ograniczoną odpowiedzialnością, KRS 0000589683, sygnatura akt WA1M/GUp/9/2025, postanowił:
+1.na mocy art. 213 ust. 1 w zw. z art. 206 ust. 1 pkt 3 ustawy z dnia 28 lutego 2003 r. Prawo upadłościowe wyrazić zgodę Syndykowi Masy Upadłości N13 spółka z ograniczoną odpowiedzialnością w Warszawie na sprzedaż z wolnej ręki należności wskazanej we wniosku z dnia 01 marca 2026 r. (numer w aktach 187), uzupełnionego pismem z dnia 24 marca 2026 r. (numer w aktach 204), na warunkach określonych w piśmie, przy uwzględnieniu zmian zawartych w niniejszym postanowieniu, które to pisma uczynić integralną częścią niniejszego postanowienia, tj.
+należności z tytułu nienależnego świadczenia na rzecz Agaty Niziałek o wartości nominalnej 66.082,53 zł (sześćdziesiąt sześć tysięcy osiemdziesiąt dwa złote pięćdziesiąt trzy grosze) - poz. 5.6. spisu inwentarza z dnia 01 marca 2026 r. (numer w aktach 186) za cenę nie niższą niż 14.869,00 zł (czternaście tysięcy osiemset sześćdziesiąt dziewięć złotych zero groszy);
+2. określić ponadto następujące dodatkowe warunki sprzedaży:
+a. sprzedaż zostanie poprzedzona ogłoszeniem podanym do publicznej wiadomości o sprzedaży w Internecie, na co najmniej trzech portalach ogólnopolskich specjalizujących się w sprzedaży lub obrocie mieniem podobnego rodzaju co mienie wskazane w pkt 1, zawierającym informacje na temat: sprzedaży wymienionych w pkt 1 składników majątkowych, formie i miejscu składania ofert oraz dane kontaktowe syndyka, pod którymi można uzyskać wszelkie niezbędne informacje na temat przedmiotu sprzedaży oraz trybu sprzedaży;
+b. syndyk dokona rozesłania informacji o konkursie ofert do potencjalnych zainteresowanych podmiotów i upubliczni informację o konkursie ofert w inny sposób, niż w pkt a) powyżej, a wynikający z własnego doświadczenia zawodowego syndyka, tak aby informacja dotarła do możliwe szerokiego grona zainteresowanych,
+c. zawarcie umowy sprzedaży z oferentem będzie możliwe nie wcześniej niż po upływie 2 (dwóch) tygodni od dnia podania do publicznej wiadomości ogłoszeń o sprzedaży przy czym bieg terminu będzie liczony od daty ukazania się późniejszego z ogłoszeń;
+d. w przypadku otrzymania przez syndyka więcej niż jednej oferty, równej cenie minimalnej, na nabycie aktywów objętych niniejszym wnioskiem, syndyk przeprowadzi konkurs ofert;
+e. koszty zawarcia umowy ponosi w całości kupujący,
+f. wybór oferty zostanie dokonany przy zastosowaniu kryterium ceny;
+g. cena zakupu powinna wpłynąć na rachunek wskazany przez syndyka nie później niż na 2 dni przed zawarciem umowy sprzedaży.
+3. wniosek o wyrażenie zgody na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości z dnia 01 marca 2026 r. (numer w aktach 187), uzupełnionego pismem z dnia 24 marca 2026 r. (numer w aktach 204), uczynić integralną częścią postanowienia.</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyODcwYjY1ODEtODU2ZC00ZDhhLTgyNWMtYjFiZjI1NzA0YTMwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>20260407/00790</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-Sędzia-upr/381/2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Kęsy</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Ryczywół, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>99010501384</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>XI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy, ul. Młyńska 1a, 61-729 Poznań, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Paulina Kęsy (PESEL 99010501384), sygnatura akt PO1P/GUp-Sędzia-upr/381/2026
+oddalić wniosek upadłej o wyłączenie z masy upadłości pojazdu FORD FOCUS C-MAX, rok produkcji 2010, numer rejestracyjny PCH6LT7, ujętego w spisie inwentarza pod numerem 1.1.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZTA5ZWU5NTYtMTRkMS00OWU2LTlkNzYtMDliMzhhOTNmNzAzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>20260407/00803</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>PO1P/GUp-Sędzia-upr/382/2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Paulina</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Kęsy</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Ryczywół, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>99010501384</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>XI Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy, ul. Młyńska 1a, 61-729 Poznań, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Paulina Kęsy (PESEL 99010501384), sygnatura akt PO1P/GUp-Sędzia-upr/382/2026
+oddalić wniosek upadłej o wyłączenie z masy upadłości przyczepki ciężarowej do przewozu zwierząt marki SAM, rok produkcji 2013r., o nr. rej. PCT08WP (składnik 1.2. w spisie inwentarza).
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Poznań-Stare Miasto w Poznaniu, XI Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNWEzZGI5ZDktZjJjNy00NDMxLTgyNmItYzEwMjM4YmM2ZjM2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>20260407/00808</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OP1O/GUp/6/2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Katarzyna</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Rossa</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Ujazd, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>94112605503</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Opolu</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Zastępca sędziego-komisarza obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza dłużnika, którym jest Katarzyna Rossa, PESEL 94112605503, prowadzonej pod sygn. akt OP1O/GUp/6/2026, postanowił:
+na podstawie art. 63 ust. 1 pkt 1 ustawy z dnia 28 lutego 2003 r. – Prawo upadłościowe w zw. z art. 829 pkt 6 k.p.c. stwierdzić, że prawo własności samochodu osobowego marki Peugeot 206 1.4, numer rejestracyjny OST 9JU4, rok produkcji 2003, nie wchodzi w skład masy upadłości;
+na podstawie art. 357 § 6 k.p.c. w zw. z art. 229 ust. 1 ustawy z dnia 28 lutego 2003 r. – Prawo upadłościowe odstąpić od uzasadnienia niniejszego postanowienia, uwzględniając w całości wniosek upadłej z dnia 5 marca 2026 roku (znak pisma: OP1O/GUp/6/2026/5) oraz podzielając argumenty upadłej oraz opinię syndyka masy upadłości (znak pisma: OP1O/GUp/6/2026/19) przytoczone na jego poparcie.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego w Opolu, V Wydział Gospodarczy Sekcja ds. Upadłościowych i Restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyODA5MmI1NDAtZmZkOC00MDAwLWIyMzYtMzNjMzViZDIzZDk2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>20260407/00810</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>KR1S/GUp/42/2025</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Stec</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kraków, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>88062113241</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5130152946</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz ( sędzia wyznaczony do roli sędziego komisarza ) obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Barbara Stec, PESEL 88062113241, sygnatura akt KR1S/GUp/42/2025, postanowił:
+1. na podstawie art. 315 p.u. w zw. z art. 334 ust. 1 p.u. w zw. z art. 151 ust. 1 b p.u. wyłączyć z masy upadłości Barbary Stec 49 ( czterdzieści dziewięć ) udziałów o łącznej wartości nominalnej 4900,00 zł w spółce ELECTRO HOUSE SOLUTION Sp. z o.o. w Krakowie, KRS:0001009719, ujętych w spisie inwentarza sporządzonym przez syndyka pod pozycją 4.1;
+2. na podstawie art. 357 § 6 k.p.c. w związku z art. 229.1 p.u. odstąpić od uzasadnienia punktu I sentencji postanowienia z uwagi na uwzględnienie w całości wniosku syndyka z dnia 4 grudnia 2025 roku, przy podzieleniu w całości argumentów przytoczonych na jego poparcie ( wniosek pod znakiem KR1S/GUp/42/2025/108) oraz wyrażonej w dniu 11 marca 2026 roku aprobacie wniosku przez pełnomocnika upadłej ( stanowisko upadłej pod znakiem 171), po rozważeniu całokształtu okoliczności sprawy, w tym mając na uwadze, iż dotychczasowe czynności ukierunkowane na likwidację objętych wnioskiem aktywów masy nie przyniosły wymiernego efektu w postaci znalezienia chętnego na nabycie udziałów, a dalsze pozostawanie tych składników na stanie masy może przyczynić się jedynie do generowanie zbędnych kosztów.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZTg5MTMwNzUtZDc2Mi00NTI1LWI0MGMtNTc0OTExZDgwZTI1JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>20260407/00816</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/27/2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Łukasz</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Gulbinowicz</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Szczecin, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>81091417890</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>8512804817</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Łukasz Gulbinowicz (PESEL 81091417890), sygnatura akt SZ1S/GUp-s/27/2026
+w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Łukasza Gulbinowicza, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZTc1YzM3MjQtOGUzNi00MTVjLThiNjMtN2M3ZGMxYWU4ZGQwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>20260407/00827</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/56/2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>KAROL</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>KOT</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Stargard, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>93052306392</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>8542385288</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Krzysztof Andrzej Kaczmarek, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest KAROL KOT (PESEL 93052306392), sygnatura akt SZ1S/GUp-s/56/2026
+obwieszcza: do akt postępowania pod sygnaturą SZ1S/GUp-s/56/2026 złożono spis inwentarza oraz plan likwidacyjny wraz z preliminiarzem wydatków.</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmVjODM3YmYtMWY4Yy00NTc4LThjYTgtNGJlOTI0NjgyNDI0JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>20260407/00832</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TO1T/GUp-Sędzia-upr/191/2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Kinga</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Domżalska</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grudziądz, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>88030604687</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Toruniu</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Toruniu, V Wydział Gospodarczy, ul. Władysława Warneńczyka 1, 87-100 Toruń, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Kinga Domżalska (PESEL 88030604687), sygnatura akt TO1T/GUp-Sędzia-upr/191/2025
+obwieszcza: na mocy orzeczenia z dnia 7 kwietnia 2026 r. sędzia wyznaczony w Sądzie Rejonowym w Toruniu postanowił:
+wyłączyć z masy upadłości Kingi Domżalskiej samochód osobowy marki Toyota Yaris, rok produkcji 2000, VIN JTDJV183300245546.
+UZASADNIENIE
+Upadła Kinga Domżalska wniosła o wyłączenie z masy upadłości samochodu osobowego. W uzasadnieniu swojego wniosku wskazała na niewielką wartość pojazdu - ok. 3.000,00 zł oraz fakt, że pojazd jest niezbędny do jej codziennego funkcjonowania oraz realizacji obowiązków rodzinnych. Upadła jest w trakcie leczenia psychiatrycznego i terapeutycznego, wymagającego regularnych dojazdów do różnych miejscowości, a dojazd komunikacją publiczną jest utrudniony i mógłby negatywnie wpływać na proces realizacji leczenia. Upadła sprawuje opiekę nad dwiema małoletnimi córkami, jedna z nich pozostaje pod opieką specjalistyczną, co wiąże się z cyklicznymi dojazdami do poradni. W ocenie upadłej, pozbawienie jej samochodu naruszałoby jej minimalny, godny poziom życia i jej dzieci, a względy humanitarne przemawiają za uwzględnieniem wniosku.
+Syndyk nie sprzeciwił się wnioskowi upadłej. Wskazał na niską wartość rynkową pojazdu – na podstawie analizy ofert sprzedaży podobnych aut określa ją na 2.600–4.000 zł. W jego ocenie koszty przechowywania, zabezpieczenia i sprzedaży samochodu mogłyby przewyższyć potencjalny zysk z jego zbycia, co oznaczałoby brak realnej korzyści dla wierzycieli. Wyłączenie pojazdu jest więc zgodne z zasadą celowości i ekonomiki postępowania upadłościowego. Syndyk podniósł, że upadła przedstawiła dokumentację medyczną potwierdzającą stan zdrowia oraz konieczność regularnych dojazdów związanych z leczeniem i opieką nad dziećmi. Samochód stanowi dla niej środek niezbędny do zaspokajania podstawowych potrzeb życiowych. Na marginesie syndyk wskazał, że masa upadłości jest zasilana regularnymi wpływami z zajęcia wynagrodzenia upadłej (dotychczas 5.246,20 zł, ok. 1.700 zł miesięcznie), co pozwala na pokrycie kosztów postępowania bez konieczności likwidacji pojazdu. Zdaniem syndyka wyłączenie samochodu z masy upadłości jest zasadne zarówno z perspektywy interesu wierzycieli, jak i sytuacji osobistej upadłej.
+Sędzia-komisarz /sędzia wyznaczony w trybie art. 4915 ust. 3 pr. up./ ustalił i zważył, co następuje:
+W niniejszej sprawie sędzia-komisarz (sędzia wyznaczony) uznał, że wniosek upadłej o wyłączenie z masy upadłości pojazdu zasadny. Pojazd faktycznie, jak wynika ze zgodnych stanowisk upadłej i syndyka, przedstawia niewielką wartość. Jest to pojazd wieloletni (26 lat) i wyeksploatowany. Ekonomiczny rezultat zbycia tego składnika majątkowego należy uznać za niewielki. Normą jest, że przy sprzedaży wymuszonej cena uzyskana jest często niższa niż wartość rynkowa rzeczy. Ponadto pozostawienie w masie upadłości samochodu wiązałoby się nieuchronnie z jego należytym utrzymaniem, wykupem niezbędnych ubezpieczeń, wykonaniem przeglądów, co w porównaniu z wartością pojazdu byłoby ekonomicznie nieuzasadnione.
+           W tym stanie rzeczy sędzia-komisarz (sędzia wyznaczony) przychylił się do wniosku i orzekł jak w sentencji na podstawie art. 315 pr. up. w zw. z art. 4912 ust. 1 pr. up.
+Od postanowienia przysługuje zażalenie w terminie 7 dni od dnia obwieszczenia.</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMTliNzkxZjgtODhmOS00ODdjLThmMWYtYjRjOWUxNWE1MjFjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>20260407/00835</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TO1T/GUp-Sędzia-upr/2/2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Małgorzata Samanta</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Wyszomirska</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Aleksandrów Kujawski, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>90090305860</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Toruniu</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Toruniu, V Wydział Gospodarczy, ul. Władysława Warneńczyka 1, 87-100 Toruń, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Małgorzata Samanta Wyszomirska (PESEL 90090305860), sygnatura akt TO1T/GUp-Sędzia-upr/2/2026
+obwieszcza: na mocy orzeczenia z dnia 7 kwietnia 2026 r. sędzia wyznaczony w Sądzie Rejonowym w Toruniu postanowił:
+wyłączyć z masy upadłości składnik majątkowy w postaci skutera SHENKE SHOTGUN, ujętego w spisie inwentarza pod numer 1.2.
+UZASADNIENIE
+Syndyk wniósł o wyłączenie z masy upadłości skutera wchodzącego w skład masy upadłości z uwagi na brak możliwości sprzedaży tego składnika majątkowego. Odbyło się kilka prób sprzedaży, które pozostały bezskuteczne. 
+Sędzia-komisarz /sędzia wyznaczony w trybie art. 4915 ust. 3 pr. up./ ustalił i zważył, co następuje:
+Wniosek należało uznać za zasadny.
+Zgodnie z art. 315 pr. up. sędzia-komisarz może wyłączyć określone składniki majątku z masy upadłości, w tym nieruchomość lub jej ułamkową część, jeżeli nie można ich zbyć z zachowaniem przepisów ustawy, a dalsze pozostawanie tych składników majątku w masie upadłości będzie niekorzystne dla wierzycieli z uwagi na obciążenie masy upadłości związanymi z tym kosztami. Przez składniki majątku, których nie można zbyć z zachowaniem przepisów ustawy, należy rozumieć te, w stosunku do których, po ich uprzednim oszacowaniu, podjęto próbę sprzedaży. Nie jest wystarczające jednokrotne wystawienie danego składnika na sprzedaż, by stwierdzić, iż jest on niesprzedawalny. Wyłączenie z masy upadłości będzie uzasadnione zwłaszcza w sytuacji, gdy likwidacja masy upadłości została w przeważającej części zakończona, a podejmowanie dalszych prób sprzedaży danego składnika prowadziłoby do przedłużenia postępowania, a co za tym idzie, do zwiększenia kosztów tego postępowania (por. M. Mozdżeń [w:] Prawo upadłościowe. Komentarz, wyd. II, red. A. J. Witosz, Warszawa 2021, art. 315).
+W niniejszej sprawie Sędzia-komisarz uznał, iż wniosek syndyka jest uzasadniony.
+Syndyk podjął kilkukrotną próbę sprzedaży składnika majątkowego, którego wartość oszacowania jest relatywnie niska – na ok. 500,00 zł. Syndyk podejmując się czynności likwidacyjnych umieścił ogłoszenia na portalu OLX oraz na profilu kancelarii w serwisie Facebook, najpierw za 100% wartości oszacowania, a następnie – wobec braku zainteresowania – za 75% tej kwoty. W pierwszym terminie nie wpłynęła żadna oferta, natomiast w drugim zgłoszono dwie propozycje (200 zł i 250 zł), które po weryfikacji stanu technicznego (który należy ocenić jako obiektywnie zły i wymagający istotnych nakładów finansowych – w szczególności wymiany akumulatora, pompy paliwa oraz naprawy tłoków w silniku) zostały cofnięte przez oferentów z uwagi na nieopłacalność napraw przewyższających wartość pojazdu. W ocenie Sędziego-komisarza należy zgodzić się ze stanowiskiem syndyka, iż pozostawienie tego składnika majątkowego w masie upadłości będzie wiązało się tylko z dodatkowymi kosztami, w tym kosztami ewentualnych dalszych ogłoszeń sprzedaży.
+           Mając powyższe na uwadze, sąd uznał że należy wyłączyć składnik majątkowy z masy upadłości. Dlatego też orzeczono jak w sentencji postanowienia na podstawie art. 315 pr. up.
+Od postanowienia przysługuje zażalenie w terminie 7 dni od dnia obwieszczenia.</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZjQ1NzkxZjctMTJkNy00NTIxLWE5ZDQtN2E0MjhjOGFhYjNhJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>20260407/00842</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/60/2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Jacek</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Burda</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Szczecin, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>63101201354</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>8511002837</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Aleksandra Brykczyńska-Grudzińska, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Jacek Burda (PESEL 63101201354), sygnatura akt SZ1S/GUp-s/60/2026
+do akt postępowania zostało złożone sprawozdanie ogólne o stanie masy upadłości i możliwości zaspokojenia wierzycieli.</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOWJiZDM4OTItNjU4Ny00OWQ2LWIwOTUtZGQzZjJiZDNkNmVjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20260407/00849</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TR1T/GUp-Sąd-upr/298/2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Anna</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Kierońska</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Tarnów, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>70022802049</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8711281960</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Tarnowie</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>V Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy w Tarnowie, V Wydział Gospodarczy, ul. Dąbrowskiego 27, 33-100 Tarnów, obwieszcza, że dokumentem z dnia 10 grudnia 2025 roku złożonym w sprawie wnioski oraz pisma do rozpoznania przez sąd w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Anna Kierońska (PESEL: 70022802049), sygnatura akt TR1T/GUp-Sąd-upr/298/2025, Syndyk zawiadomił o sposobie likwidacji stanowiącego odrębną nieruchomość lokalu mieszkalnego numer 10, położonego na parterze budynku numer 12 przy ulicy Bolesława Prusa w Tarnowie, dla którego Sąd Rejonowy w Tarnowie, VI Wydział Ksiąg Wieczystych prowadzi księgę wieczystą numer TR1T/00116720/5.</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzQ5YjAzOTAtY2E0NS00OGI2LThmNTQtNmVkYmQ4MThhNWRlJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20260407/00851</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LU1S/GUp-s/64/2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Biegański</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Hańsk Pierwszy, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>73032906875</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>9930537578</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>sygn. akt LU1S/GUp-s/64/2025, znak pisma: LU1S/GUp-s/64/2025/62
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Mariusz Biegański, prowadzonego pod sygn. akt: LU1S/GUp-s/64/2025, złożono do akt opis i szacowanie:
+nieruchomości: udziału wynoszącego 1/2 w nieruchomości gruntowej stanowiącej przedmiot prawa własności zabudowanej budynkiem mieszkalnym z towarzyszącą zabudową gospodarczą położonej przy ulicy Parczewskiej 28 w miejscowości Hańsk Pierwszy, powiat włodawski. Opis i oszacowanie jest dostępny w aktach sprawy o sygn. akt LU1S/GUp-s/64/2025 (dokument nr 56)</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYzA0NDg5NmQtY2UyNi00YTdlLThiMjYtNjRmMjkzNTg3NjlmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20260407/00852</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/62/2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Mateuszczyk</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Barnimie, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>58073006803</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>8511006290</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Krzysztof Andrzej Kaczmarek, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Barbara Mateuszczyk (PESEL 58073006803), sygnatura akt SZ1S/GUp-s/62/2026
+obwieszcza: do akt postępowania SZ1S/GUp-s/62/2026 syndyk złożył spis inwentarza oraz plan likwidacyjny wraz z preliminarzem wydatków.</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOWY2YjhhZDEtZjYyZC00OTcwLTlkY2UtZmVkNTNlZmZmODcwJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>20260407/00853</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LU1S/GUp-s/64/2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Mariusz</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Biegański</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Hańsk Pierwszy, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>73032906875</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>9930537578</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>sygn. akt LU1S/GUp-s/64/2025, znak pisma: LU1S/GUp-s/64/2025/66
+Treść obwieszczenia syndyka
+Dnia 7 kwietnia 2026 roku
+Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Mariusz Biegański, prowadzonego pod sygn. akt: LU1S/GUp-s/64/2025, złożono do akt opis i szacowanie:
+nieruchomości: udziału wynoszącego 1/2 w nieruchomości gruntowej stanowiącej przedmiot prawa własności zabudowanej budynkiem mieszkalnym z towarzyszącą zabudową gospodarczą położonej przy ulicy Parczewskiej 28 w miejscowości Hańsk Pierwszy, powiat włodawski. Opis i oszacowanie jest dostępny w aktach sprawy o sygn. akt LU1S/GUp-s/64/2025 (dokument nr 56)
+Poucza się, że na opis i oszacowanie można wnieść zarzuty. Zarzuty wnosi się w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia sędziemu-komisarzowi albo w przypadku postępowania upadłościowego prowadzonego na podstawie art. 491 (1) ust. 1 prawa upadłościowego sędziemu wyznaczonemu.</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMGFlNGRjZTQtYzE2Zi00MjgyLTg1YzktZmRlNTc1OGQyYjMxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20260407/00855</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LD1M/GUp/9/2022</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Ryszard</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Biesaga</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Łódź, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>74012906894</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>7311336987</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy dla Łodzi-Śródmieścia w Łodzi</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>XIV Wydział Gospodarczy ds. Upadłościowych i Restrukturyzacyjnych</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Ryszard Biesaga, PESEL 74012906894, sygnatura akt LD1M/GUp/9/2022, postanowił:
+na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki mienia wchodzącego w skład masy upadłości w postaci spółdzielczego własnościowego prawa do lokalu położonego w Pabianicach przy ul. Drewnowskiej 47 m 37, dla którego Sąd Rejonowy w Pabianicach V Wydział Ksiąg Wieczystych prowadzi księgę wieczystą o nr LD1P/ 00041543/ 4, numer składnika masy upadłości w spisie inwentarza - 2.1,
+określić następujące warunki sprzedaży:
+a/ sprzedaż zostanie przeprowadzona w drodze konkursu ofert,
+b/ cena wywoławcza wynosić będzie 280.000 zł (dwieście osiemdziesiąt tysięcy złotych),
+c/ termin na składanie ofert będzie wynosił co najmniej dwa tygodnie od daty ogłoszenia o konkursie ofert,
+d/ ogłoszenie o konkursie ofert zostanie zamieszczone co najmniej w dwóch portalach internetowych zamieszczających ogłoszenia o sprzedaży nieruchomości,
+e/ wyboru oferty dokona syndyk, a w razie powołania – komisja,
+f/ cena sprzedaży udziału powinna być wpłacona i zaksięgowana na koncie masy upadłości najpóźniej w dniu zawarcia umowy,
+g/ wszelkie koszty zawarcia umowy sprzedaży obciążają nabywcę.</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTdkYTczYzItMTZiMi00OGQ1LTlmOTEtMzEzMTIxNmJmNjM0JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>20260407/00856</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SZ1S/GUp-s/63/2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Adam</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Ciwiński</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Płotno, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>69051209714</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5981257409</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Syndyk, którym jest Krzysztof Andrzej Kaczmarek, obwieszcza, że dokumentem z dnia 7 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Adam Ciwiński (PESEL 69051209714), sygnatura akt SZ1S/GUp-s/63/2026
+obwieszcza: do akt postępowania SZ1S/GUp-s/63/2026 syndyk złożył spis inwentarza oraz plan likwidacyjny wraz z preliminarzem wydatków.</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMjVhY2MyODMtZGM4Yy00NDQ3LWJiYjMtNTc4MjVkMzFmZTg3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>20260407/00864</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LD1M/GUp-s/710/2024</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Paweł</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Pawlak</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Uników, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>87081814230</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>8272173664</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Dorota Borkowska - Syndyk masy upadłości Pawła Pawlak (PESEL: 87081814230, NIP: 8272173664), jako osoby fizycznej nieprowadzącej działalności gospodarczej, obwieszcza, że w toku postępowania upadłościowego prowadzonego za sygnaturą akt LD1M/GUp-s/710/2024 sporządzono i złożono do akt sprawy opis i oszacowanie wchodzącego w skład masy upadłości prawa własności niezabudowanej nieruchomości gruntowej poł. w miejscowości: Uników (gm. Złoczew, powiat: sieradzki, woj.: łódzkie) składającej się z działki ewidencyjnej: dz. nr 174 o pow. 9 900 m², dla której Sąd Rejonowy w Sieradzu prowadzi księgę wieczystą: SR1S/00071669/9.
+Opis i oszacowanie wskazanego powyżej prawa własności nieruchomości są dostępne w aktach sprawy LD1M/GUp-s/710/2024 (dokument nr LD1M/GUp-s/710/2024/22). 
+Zarzuty na złożony w aktach opis i oszacowanie można wnosić w terminie tygodnia od dnia ukazania się niniejszego obwieszczenia. Zarzuty wnosi się na piśmie 70008 „Pismo inne”. Wypełniając formularz nie należy wypełniać pozycji sygnatura, ponieważ podanie sygnatury LD1M/GUp-s/710/2024 spowoduje, że zarzuty zostaną jedynie dołączone do akt postępowania prowadzonych przez syndyka, natomiast nie będą widoczne dla Sądu nadzorującego postępowanie upadłościowe. W uzasadnieniu pisma (zarzutów) należy wskazać, że sprawę prowadzi syndyk za sygnaturą LD1M/GUp-s/710/2024. Zarzuty rozpoznaje Sędzia wyznaczony. W przypadku wątpliwości co do rzetelności lub poprawności opisu i oszacowania, sędzia wyznaczony wskazuje biegłego do sporządzenia nowego opisu i oszacowania.</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyN2QwYTNiMWEtZTU2ZC00MjAzLTk3MDYtMmZhN2YzYzkzZTc2JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>20260407/00874</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>07.04.2026</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>KA1K/GUp-Sędzia-upr/55/2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Bartosz</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Filipek</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Sosnowiec, Polska / POLAND</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>97010601356</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Katowice Wschód w Katowicach</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>X Wydział Gospodarczy</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Sąd Rejonowy Katowice Wschód w Katowicach, X Wydział Gospodarczy, ul. Józefa Lompy 14, 40-040 Katowice, obwieszcza, że postanowieniem z dnia 7 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Bartosz Filipek (PESEL 97010601356), sygnatura akt KA1K/GUp-Sędzia-upr/55/2026, postanowił:
+wyłączyć z masy upadłości upadłej Bartosza Filipka wierzytelność o zapłatę należności z tytułu zaległego wynagrodzenia za pracę przysługującą upadłemu względem Ireneusza Pięty (numer 5.1 w spisie inwentarza);
+na podstawie art. 357 § 6 k.p.c. w zw. z art. 229 ust. 1 i art. 4912 ust. 1 ustawy z dnia 28 lutego 2003 roku – Prawo upadłościowe (tekst jedn. Dz. U. z 2025 r., poz. 614) odstąpić od uzasadnienia postanowienia, wobec uwzględnienia w całości wniosku syndyka o wyłączenie z masy upadłości oraz podzielenia argumentacji przytoczonej na jego poparcie.
+Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Katowice-Wschód w Katowicach, X Wydział Gospodarczy. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZjZmMWJiODYtMDhhMi00OGU3LThkYjgtZDlmZmJkMzI4NGY4JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>20260406/00017</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>SZ1S/GUp-s/61/2026</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Zbigniew</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>Banach</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Uniemyśl, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
         <is>
           <t>54032407177</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>8512599352</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
         <is>
           <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
 obwieszcza:
 w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
         </is>
       </c>
-      <c r="M26" s="2" t="inlineStr">
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNzFjOWJmN2YtOTE1MS00YjRhLTg2NDYtYmY2ZWRlNTA4YWE3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>20260406/00019</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>SZ1S/GUp-s/61/2026</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Zbigniew</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>Banach</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>Uniemyśl, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
         <is>
           <t>54032407177</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>8512599352</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
         <is>
           <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Zbigniew Banach (PESEL 54032407177), sygnatura akt SZ1S/GUp-s/61/2026
 obwieszcza:
 w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Zbigniewa Banacha osoby fizycznej nieprowadzącej działalności gospodarczej, został złożony następujący dokument: korekta planu likwidacyjnego.</t>
         </is>
       </c>
-      <c r="M27" s="2" t="inlineStr">
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTNlMWYzOTUtMDQ5Ny00MGNjLTliNDUtMzRjNTRiNDllMTkxJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>20260406/00021</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>SZ1S/GUp-s/64/2026</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Agata</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>Cudzanowska</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>Szczecin, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>82070118148</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
         <is>
           <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Agata Cudzanowska (PESEL 82070118148), sygnatura akt SZ1S/GUp-s/64/2026
 obwieszcza:
 w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Agaty Cudzanowskiej, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTYwNzc1YjMtNzQyZi00YTBlLTkxNWUtYTAwZjI5MzI5YTU3JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>20260406/00031</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>SZ1S/GUp-s/68/2026</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Agnieszka</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>Musialska</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>Dębina, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
         <is>
           <t>67122407780</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>8521357134</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
         <is>
           <t>Syndyk, którym jest Monika Borek, obwieszcza, że dokumentem z dnia 6 kwietnia 2026 roku wydanym w sprawie sprawy po ogłoszeniu upadłości osób fizycznych nieprowadzących działalności gospodarczej prowadzone przez syndyka dłużnika, którym jest Agnieszka Musialska (PESEL 67122407780), sygnatura akt SZ1S/GUp-s/68/2026
 obwieszcza:
 w trybie przepisu art. 219 ust. 1d ustawy Prawo upadłościowe, że do akt postępowania upadłościowego Agnieszki Musialskiej, osoby fizycznej nieprowadzącej działalności gospodarczej, zostały złożone następujące dokumenty: spis inwentarza oraz plan likwidacyjny.</t>
         </is>
       </c>
-      <c r="M29" s="2" t="inlineStr">
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyOTExNGMyNTYtNWM1Zi00ZmExLWEyMWEtM2I3MzU0MmRkMmVmJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>20260406/00032</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>CZ1C/GUp-s/168/2024</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Krzysztof</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>Grudziński</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>Pawonków, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
         <is>
           <t>83110518775</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
         <is>
           <t>sygn. akt CZ1C/GUp-s/168/2024, znak pisma: CZ1C/GUp-s/168/2024/32
 Treść obwieszczenia syndyka
@@ -2460,61 +5755,61 @@
 Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWYxMjljOTMtMDU2NC00NDgwLTk4MzktNTFlMTk1YTczMGZkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>20260406/00033</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>CZ1C/GUp-s/243/2025</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Stanisław</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Najgebauer</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>Zawada, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>47050802053</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>5730037834</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
         <is>
           <t>sygn. akt CZ1C/GUp-s/243/2025, znak pisma: CZ1C/GUp-s/243/2025/16
 Treść obwieszczenia syndyka
@@ -2531,61 +5826,61 @@
 Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyODlkYjkwOTktYmEzOC00NWM2LWI0OTEtNDMxNDVlNzYxZWVkJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>20260406/00045</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>BB1B/GUp-s/513/2025</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Grzegorz</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Ziemba</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Hecznarowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
         <is>
           <t>90032314833</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>9372507846</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
         <is>
           <t>sygn. akt BB1B/GUp-s/513/2025, znak pisma: BB1B/GUp-s/513/2025/27
 Treść obwieszczenia syndyka
@@ -2593,61 +5888,61 @@
 Syndyk obwieszcza, że w postępowaniu upadłościowym dłużnika, którym jest Grzegorz Ziemba, prowadzonego pod sygn. akt: BB1B/GUp-s/513/2025, złożono do akt opis i szacowanie udziału wynoszącego 1/8 w prawie własności nieruchomości położonej w Hecznarowicach, gmina Wilamowice, powiat bielski, dla której Sąd Rejonowy w Bielsku-Białej, VII Wydział Ksiąg Wieczystych prowadzi księgę wieczystą nr BB1B/00088834/2, składającej się z działek ewidencyjnych o numerach: 2102 o pow. 0,0972 ha zabudowanej budynkiem mieszkalnym nr 64 przy ul. Stawowej, 26/3 o pow. 0,0421 ha zabudowanej dwoma budynkami niemieszkalnymi (gospodarczymi) oraz 26/12 o pow. 0,1503 ha niezabudowanej</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMWYyZGYzNTEtMmI5OC00NjFiLTg5NTQtNWZlNGQ0NzE2ZDZjJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>20260406/00050</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>06.04.2026</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>LD1M/GUp-s/846/2025</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Izabela</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Jurczyk</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Łódź, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>74070301321</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>7262141998</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
         <is>
           <t>sygn. akt LD1M/GUp-s/846/2025, znak pisma: LD1M/GUp-s/846/2025/60
 Treść obwieszczenia syndyka
@@ -2664,204 +5959,204 @@
 Możesz również w katalogu dokumentów nacisnąć przycisk "Wyszukaj wzór pisma" i w polu wyszukiwania wpisać . W wynikach wyszukiwania należy wybrać najwyższą wersję pisma.</t>
         </is>
       </c>
-      <c r="M33" s="2" t="inlineStr">
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYTU2OGJiNTktYTE5OS00YjBiLTgzYzQtZWMzZWVmMGE0MDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>20260405/00001</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>05.04.2026</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>KR1S/GUp/88/2024</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Jakubowska</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>Skawina, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>84020202589</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>6751275485</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 5 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Katarzyna Jakubowska, PESEL 84020202589, sygnatura akt KR1S/GUp/88/2024, na podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolił syndykowi na sprzedaż z wolnej ręki, po obniżonej cenie, udziału w wysokości 1/2 w prawie własności nieruchomości gruntowej położonej w przy ul. Armii Krajowej 18 w miejscowości Skawina, gm. Skawina, woj. małopolskie, obejmującej działki ewidencyjne nr 5644 i 5645, dla której Sąd Rejonowy w Wieliczce V Zamiejscowy Wydział Ksiąg Wieczystych z s. w Skawinie prowadzi księgę wieczystą nr KR3I/00008006/0 (nr 2.1 w spisie inwentarza), za najwyższą zaoferowaną cenę, nie niższą niż 250.687,50 zł (dwieście pięćdziesiąt tysięcy sześćset osiemdziesiąt siedem złotych 50/100) po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej trzy tygodnie przed terminem rozstrzygnięcia konkursu na co najmniej trzech internetowych portalach branżowych.</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjRkOWFkY2YtNjVmZC00NjNkLWJhNGItNGNjOWVmOGUxYjMyJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>20260404/00007</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>KR1S/GUp-Sędzia-upr/12/2026</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>Katarzyna</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Jachyra</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>Piotrowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
         <is>
           <t>76032018700</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>5492062327</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Katarzyna Jachyra (PESEL 76032018700), sygnatura akt KR1S/GUp-Sędzia-upr/12/2026
 obwieszcza: że w skład masy upadłości nie wchodzi wynagrodzenie upadłej Katarzyny Jachyry w całości, począwszy od miesiąca marca 2026 roku.</t>
         </is>
       </c>
-      <c r="M35" s="2" t="inlineStr">
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyMmJkYzg3ZTgtNjM0ZS00MjE3LWI2ZjUtNzRiNzhhNWNhMDhiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>20260404/00012</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>LU1S/GUp-Sędzia-upr/46/2026</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Łukasz</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Maciąg</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>Orchówek, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
         <is>
           <t>77110706933</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>5791764391</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Sąd Rejonowy Lublin-Wschód w Lublinie z siedzibą w Świdniku</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie wnioski oraz pisma do rozpoznania przez sędziego wyznaczonego w sprawach upadłościowych osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Łukasz Maciąg , PESEL 77110706933, sygnatura akt LU1S/GUp-Sędzia-upr/46/2026, postanowił:
 I.               wyłączyć z masy upadłości Łukasza Maciąga jako osoby fizycznej nieprowadzącej działalności gospodarczej prawa majątkowe w postaci 100 udziałów w spółce LUBAVA SPÓŁKA Z OGRANICZONĄ ODPOWIEDZIALNOŚCIĄ z siedzibą w Warszawie, KRS: 0000620127, o wartości nominalnej 5000 zł (poz. 4.1 spisu inwentarza LU1S/GUp-s/232/2024/154);
@@ -2869,65 +6164,65 @@
 Na niniejsze postanowienie przysługuje zażalenie do Sądu Rejonowego Lublin-Wschód w Lublinie z siedzibą w Świdniku, IX Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych. Zażalenie należy wnieść w ciągu tygodnia od dnia obwieszczenia postanowienia w Rejestrze. Zażalenie podlega opłacie w wysokości 200,00 zł.</t>
         </is>
       </c>
-      <c r="M36" s="2" t="inlineStr">
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyNjY4ODQ3ZjEtNDM1YS00NDQwLTgwNjQtY2FhMWE3NTdiNTRiJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>20260404/00018</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>KR1S/GUp-Sędzia-upr/860/2025</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Małgorzata</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Borkowicz</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>Kraków, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
         <is>
           <t>72073114968</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie, VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych, ul. Przy Rondzie 7, 31-547 Kraków, obwieszcza, że postanowieniem z 4 kwietnia 2026 roku wydanym w sprawie upadłościowej osób fizycznych nieprowadzących działalności gospodarczej dłużnika, którym jest Małgorzata Borkowicz (PESEL 72073114968), sygnatura akt KR1S/GUp-Sędzia-upr/860/2025
 obwieszcza:
@@ -2935,70 +6230,70 @@
 II. ustalić, że w skład masy upadłości nie wchodzą środki zgromadzone na rachunku depozytowym Domu Pomocy Społecznej przy ul. Łanowej 1B w Krakowie w kwocie 2 555,27 zł.</t>
         </is>
       </c>
-      <c r="M37" s="2" t="inlineStr">
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyZWU0YWI0ZjItNjhjMi00ZWFlLTk4YjMtYzQxYjcyNDY5ZjE5JTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>20260404/00026</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>04.04.2026</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>KR1S/GUp/98/2025</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Edyta</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Pułecka</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>Spytkowice, Polska / POLAND</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Osoba fizyczna nieprowadząca działalności gospodarczej</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
         <is>
           <t>76042612080</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
         <is>
           <t>Sąd Rejonowy dla Krakowa-Śródmieścia w Krakowie</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>VIII Wydział Gospodarczy dla spraw upadłościowych i restrukturyzacyjnych</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>Sędzia-komisarz obwieszcza, że postanowieniem z dnia 4 kwietnia 2026 roku wydanym w sprawie po ogłoszeniu upadłości osoby fizycznej nieprowadzącej działalności gospodarczej z udziałem sędziego-komisarza upadłego, którym jest Edyta Pułecka , PESEL 76042612080, sygnatura akt KR1S/GUp/98/2025, postanowił podstawie art. 206 ust. 1 pkt 3 w zw. z art. 213 ust. 1 ustawy z dnia 28 lutego 2003r. Prawo upadłościowe zezwolić syndykowi na sprzedaż z wolnej ręki, mienia wchodzącego w skład masy upadłości w postaci udziału w wysokości 1/2 części w prawie własności nieruchomości gruntowej zabudowanej, składającej się z działki ewidencyjnej nr 4883/34, o powierzchni 0,0655 ha, położonej w Spytkowicach, woj. małopolskie, objętej księgą wieczystą numer KR1W/00039427/1, za najwyższą zaoferowaną cenę, nie niższą niż wartość oszacowania tj. za kwotę nie niższą niż 318.000,00 zł (trzysta osiemnaście tysięcy złotych 00/100), po przeprowadzeniu przez syndyka pisemnego konkursu ofert, o którym obwieści na co najmniej dwa tygodnie przed terminem rozstrzygnięcia konkursu w prasie o zasięgu lokalnym oraz na co najmniej dwóch internetowych portalach branżowych.</t>
         </is>
       </c>
-      <c r="M38" s="2" t="inlineStr">
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>https://krz.ms.gov.pl/#!/application/KRZPortalPUB/1.9/KrzRejPubGui.SzczegolyObwieszczenia?params=JTdCJTIyaWRaZXduZXRyem55JTIyJTNBJTIyYjU3MWM5NzItYzE3Ni00Yzc2LTliNWItODJkZDFhMzBiMmYzJTIyJTJDJTIydWtyeWpXc3RlY3olMjIlM0F0cnVlJTdE</t>
         </is>
@@ -3043,6 +6338,57 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M89" r:id="rId88"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
